--- a/results/prediction_results.xlsx
+++ b/results/prediction_results.xlsx
@@ -547,61 +547,61 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>560321</v>
+        <v>101121</v>
       </c>
       <c r="D2" t="n">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>93</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="G2" t="n">
-        <v>12</v>
+        <v>47</v>
       </c>
       <c r="H2" t="n">
-        <v>81</v>
+        <v>35</v>
       </c>
       <c r="I2" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="J2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N2" t="n">
         <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P2" t="n">
-        <v>40</v>
+        <v>0.967741935483871</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>1.765957446808511</v>
       </c>
       <c r="R2" t="n">
-        <v>6.75</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="S2" t="n">
-        <v>5.748437674566498</v>
+        <v>5.004845650538529</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7547020230437259</v>
+        <v>0.974001750371997</v>
       </c>
     </row>
     <row r="3">
@@ -616,34 +616,34 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>464708</v>
+        <v>319337</v>
       </c>
       <c r="D3" t="n">
-        <v>62</v>
+        <v>91</v>
       </c>
       <c r="E3" t="n">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="F3" t="n">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="G3" t="n">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="H3" t="n">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="I3" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="J3" t="n">
         <v>6</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
         <v>1</v>
@@ -655,22 +655,22 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1.215686274509804</v>
+        <v>2.166666666666667</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.9056603773584906</v>
+        <v>0.2786885245901639</v>
       </c>
       <c r="R3" t="n">
-        <v>4.785714285714286</v>
+        <v>2.739130434782609</v>
       </c>
       <c r="S3" t="n">
-        <v>5.667181083523602</v>
+        <v>5.50425060099596</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>0.9777573397254929</v>
+        <v>0.9203672994920011</v>
       </c>
     </row>
     <row r="4">
@@ -685,28 +685,28 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>552361</v>
+        <v>374529</v>
       </c>
       <c r="D4" t="n">
+        <v>32</v>
+      </c>
+      <c r="E4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F4" t="n">
+        <v>20</v>
+      </c>
+      <c r="G4" t="n">
+        <v>65</v>
+      </c>
+      <c r="H4" t="n">
         <v>56</v>
       </c>
-      <c r="E4" t="n">
-        <v>38</v>
-      </c>
-      <c r="F4" t="n">
-        <v>25</v>
-      </c>
-      <c r="G4" t="n">
-        <v>13</v>
-      </c>
-      <c r="H4" t="n">
-        <v>10</v>
-      </c>
       <c r="I4" t="n">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="J4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K4" t="n">
         <v>2</v>
@@ -715,7 +715,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -724,22 +724,22 @@
         <v>1</v>
       </c>
       <c r="P4" t="n">
-        <v>1.473684210526316</v>
+        <v>3.2</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.923076923076923</v>
+        <v>0.3076923076923077</v>
       </c>
       <c r="R4" t="n">
-        <v>0.1923076923076923</v>
+        <v>1.365853658536585</v>
       </c>
       <c r="S4" t="n">
-        <v>5.742223793443937</v>
+        <v>5.57348661058725</v>
       </c>
       <c r="T4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>0.9497647489294363</v>
+        <v>0.233067825236852</v>
       </c>
     </row>
     <row r="5">
@@ -754,31 +754,31 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>450702</v>
+        <v>826810</v>
       </c>
       <c r="D5" t="n">
-        <v>46</v>
+        <v>8</v>
       </c>
       <c r="E5" t="n">
-        <v>37</v>
+        <v>91</v>
       </c>
       <c r="F5" t="n">
-        <v>74</v>
+        <v>47</v>
       </c>
       <c r="G5" t="n">
-        <v>93</v>
+        <v>24</v>
       </c>
       <c r="H5" t="n">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="I5" t="n">
-        <v>90</v>
+        <v>62</v>
       </c>
       <c r="J5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L5" t="n">
         <v>1</v>
@@ -787,28 +787,28 @@
         <v>1</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.243243243243243</v>
+        <v>0.08791208791208792</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.7956989247311828</v>
+        <v>1.958333333333333</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3777777777777778</v>
+        <v>0.1129032258064516</v>
       </c>
       <c r="S5" t="n">
-        <v>5.653890448861103</v>
+        <v>5.917406245903391</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9912169392524908</v>
+        <v>0.8039822054527148</v>
       </c>
     </row>
     <row r="6">
@@ -823,61 +823,61 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>29350</v>
+        <v>387617</v>
       </c>
       <c r="D6" t="n">
-        <v>17</v>
+        <v>67</v>
       </c>
       <c r="E6" t="n">
-        <v>4</v>
+        <v>48</v>
       </c>
       <c r="F6" t="n">
-        <v>5</v>
+        <v>66</v>
       </c>
       <c r="G6" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="H6" t="n">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="J6" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P6" t="n">
-        <v>4.25</v>
+        <v>1.395833333333333</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.06578947368421052</v>
+        <v>0.8354430379746836</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.21875</v>
       </c>
       <c r="S6" t="n">
-        <v>4.467622902417825</v>
+        <v>5.588403936384826</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>0.7804883155990752</v>
+        <v>0.9934238766222327</v>
       </c>
     </row>
     <row r="7">
@@ -892,31 +892,31 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>615958</v>
+        <v>645839</v>
       </c>
       <c r="D7" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>43</v>
+        <v>84</v>
       </c>
       <c r="F7" t="n">
-        <v>78</v>
+        <v>25</v>
       </c>
       <c r="G7" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I7" t="n">
-        <v>98</v>
+        <v>70</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -928,25 +928,25 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.302325581395349</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.228571428571429</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1</v>
+        <v>1.414285714285714</v>
       </c>
       <c r="S7" t="n">
-        <v>5.789551805238522</v>
+        <v>5.810124939475361</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5586126353665994</v>
+        <v>0.7994212530862147</v>
       </c>
     </row>
     <row r="8">
@@ -961,37 +961,37 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>711081</v>
+        <v>739645</v>
       </c>
       <c r="D8" t="n">
-        <v>13</v>
+        <v>94</v>
       </c>
       <c r="E8" t="n">
-        <v>11</v>
+        <v>70</v>
       </c>
       <c r="F8" t="n">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="G8" t="n">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="H8" t="n">
-        <v>59</v>
+        <v>84</v>
       </c>
       <c r="I8" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="J8" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
         <v>1</v>
@@ -1000,22 +1000,22 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.181818181818182</v>
+        <v>1.342857142857143</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.55</v>
+        <v>1.193548387096774</v>
       </c>
       <c r="R8" t="n">
-        <v>2.36</v>
+        <v>4.941176470588236</v>
       </c>
       <c r="S8" t="n">
-        <v>5.851919685250287</v>
+        <v>5.869023912931881</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
       </c>
       <c r="U8" t="n">
-        <v>0.8904703567466136</v>
+        <v>0.9711985708427222</v>
       </c>
     </row>
     <row r="9">
@@ -1030,61 +1030,61 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>796922</v>
+        <v>698511</v>
       </c>
       <c r="D9" t="n">
-        <v>91</v>
+        <v>24</v>
       </c>
       <c r="E9" t="n">
-        <v>64</v>
+        <v>24</v>
       </c>
       <c r="F9" t="n">
-        <v>28</v>
+        <v>70</v>
       </c>
       <c r="G9" t="n">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="H9" t="n">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="I9" t="n">
-        <v>19</v>
+        <v>60</v>
       </c>
       <c r="J9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.421875</v>
+        <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.9655172413793104</v>
+        <v>1.627906976744186</v>
       </c>
       <c r="R9" t="n">
-        <v>3.842105263157895</v>
+        <v>1.05</v>
       </c>
       <c r="S9" t="n">
-        <v>5.901416361182059</v>
+        <v>5.844173871422308</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>0.9331628424839482</v>
+        <v>0.9671625806264559</v>
       </c>
     </row>
     <row r="10">
@@ -1099,34 +1099,34 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>920017</v>
+        <v>229293</v>
       </c>
       <c r="D10" t="n">
-        <v>35</v>
+        <v>82</v>
       </c>
       <c r="E10" t="n">
         <v>61</v>
       </c>
       <c r="F10" t="n">
-        <v>72</v>
+        <v>93</v>
       </c>
       <c r="G10" t="n">
-        <v>82</v>
+        <v>46</v>
       </c>
       <c r="H10" t="n">
-        <v>76</v>
+        <v>48</v>
       </c>
       <c r="I10" t="n">
-        <v>13</v>
+        <v>62</v>
       </c>
       <c r="J10" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="K10" t="n">
         <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M10" t="n">
         <v>1</v>
@@ -1138,22 +1138,22 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>0.5737704918032787</v>
+        <v>1.344262295081967</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.8780487804878049</v>
+        <v>2.021739130434783</v>
       </c>
       <c r="R10" t="n">
-        <v>5.846153846153846</v>
+        <v>0.7741935483870968</v>
       </c>
       <c r="S10" t="n">
-        <v>5.963796324328383</v>
+        <v>5.360392690573881</v>
       </c>
       <c r="T10" t="n">
         <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>0.9914890667291439</v>
+        <v>0.8050769382765671</v>
       </c>
     </row>
     <row r="11">
@@ -1168,61 +1168,61 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>506876</v>
+        <v>672417</v>
       </c>
       <c r="D11" t="n">
-        <v>62</v>
+        <v>22</v>
       </c>
       <c r="E11" t="n">
-        <v>67</v>
+        <v>35</v>
       </c>
       <c r="F11" t="n">
-        <v>95</v>
+        <v>21</v>
       </c>
       <c r="G11" t="n">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="H11" t="n">
-        <v>94</v>
+        <v>53</v>
       </c>
       <c r="I11" t="n">
-        <v>98</v>
+        <v>68</v>
       </c>
       <c r="J11" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K11" t="n">
         <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M11" t="n">
         <v>1</v>
       </c>
       <c r="N11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>0.9253731343283582</v>
+        <v>0.6285714285714286</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.130952380952381</v>
+        <v>0.2142857142857143</v>
       </c>
       <c r="R11" t="n">
-        <v>0.9591836734693877</v>
+        <v>0.7794117647058824</v>
       </c>
       <c r="S11" t="n">
-        <v>5.704902585167562</v>
+        <v>5.827639330579514</v>
       </c>
       <c r="T11" t="n">
         <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>0.9961209264606946</v>
+        <v>0.9889580004939448</v>
       </c>
     </row>
     <row r="12">
@@ -1237,61 +1237,61 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>390364</v>
+        <v>567547</v>
       </c>
       <c r="D12" t="n">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="E12" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="F12" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G12" t="n">
-        <v>55</v>
+        <v>14</v>
       </c>
       <c r="H12" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="I12" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J12" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K12" t="n">
         <v>2</v>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P12" t="n">
-        <v>4.571428571428571</v>
+        <v>2.548387096774194</v>
       </c>
       <c r="Q12" t="n">
-        <v>1</v>
+        <v>3.714285714285714</v>
       </c>
       <c r="R12" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.8243243243243243</v>
       </c>
       <c r="S12" t="n">
-        <v>5.591470872036986</v>
+        <v>5.754002597589535</v>
       </c>
       <c r="T12" t="n">
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>0.8585783576003417</v>
+        <v>0.8722313766636141</v>
       </c>
     </row>
     <row r="13">
@@ -1306,31 +1306,31 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>614092</v>
+        <v>133152</v>
       </c>
       <c r="D13" t="n">
-        <v>26</v>
+        <v>82</v>
       </c>
       <c r="E13" t="n">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="F13" t="n">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="G13" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="H13" t="n">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="I13" t="n">
-        <v>12</v>
+        <v>91</v>
       </c>
       <c r="J13" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="K13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1339,28 +1339,28 @@
         <v>1</v>
       </c>
       <c r="N13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>0.4333333333333333</v>
+        <v>1.863636363636364</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.8717948717948718</v>
+        <v>1.837837837837838</v>
       </c>
       <c r="R13" t="n">
-        <v>4.833333333333333</v>
+        <v>0.7582417582417582</v>
       </c>
       <c r="S13" t="n">
-        <v>5.788234146920192</v>
+        <v>5.124350955745056</v>
       </c>
       <c r="T13" t="n">
         <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>0.9651238999842726</v>
+        <v>0.9581069081673526</v>
       </c>
     </row>
     <row r="14">
@@ -1375,34 +1375,34 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>578435</v>
+        <v>333625</v>
       </c>
       <c r="D14" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="E14" t="n">
         <v>11</v>
       </c>
       <c r="F14" t="n">
-        <v>79</v>
+        <v>38</v>
       </c>
       <c r="G14" t="n">
-        <v>96</v>
+        <v>70</v>
       </c>
       <c r="H14" t="n">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="I14" t="n">
-        <v>26</v>
+        <v>99</v>
       </c>
       <c r="J14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1414,22 +1414,22 @@
         <v>1</v>
       </c>
       <c r="P14" t="n">
-        <v>0.5454545454545454</v>
+        <v>2.727272727272727</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.8229166666666666</v>
+        <v>0.5428571428571428</v>
       </c>
       <c r="R14" t="n">
-        <v>2.038461538461538</v>
+        <v>0.4545454545454545</v>
       </c>
       <c r="S14" t="n">
-        <v>5.762255314222185</v>
+        <v>5.523259888538033</v>
       </c>
       <c r="T14" t="n">
         <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3499126459772876</v>
+        <v>0.1451104670727787</v>
       </c>
     </row>
     <row r="15">
@@ -1444,61 +1444,61 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>116211</v>
+        <v>213223</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>19</v>
       </c>
       <c r="E15" t="n">
         <v>69</v>
       </c>
       <c r="F15" t="n">
-        <v>83</v>
+        <v>27</v>
       </c>
       <c r="G15" t="n">
-        <v>92</v>
+        <v>35</v>
       </c>
       <c r="H15" t="n">
-        <v>74</v>
+        <v>12</v>
       </c>
       <c r="I15" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J15" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1.144927536231884</v>
+        <v>0.2753623188405797</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.9021739130434783</v>
+        <v>0.7714285714285715</v>
       </c>
       <c r="R15" t="n">
-        <v>4.625</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S15" t="n">
-        <v>5.065250975426973</v>
+        <v>5.328836086287675</v>
       </c>
       <c r="T15" t="n">
         <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>0.9864758558856872</v>
+        <v>0.9389643186548919</v>
       </c>
     </row>
     <row r="16">
@@ -1513,61 +1513,61 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>77374</v>
+        <v>319262</v>
       </c>
       <c r="D16" t="n">
-        <v>94</v>
+        <v>46</v>
       </c>
       <c r="E16" t="n">
-        <v>44</v>
+        <v>82</v>
       </c>
       <c r="F16" t="n">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="G16" t="n">
-        <v>11</v>
+        <v>85</v>
       </c>
       <c r="H16" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="I16" t="n">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="J16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O16" t="n">
         <v>1</v>
       </c>
       <c r="P16" t="n">
-        <v>2.136363636363636</v>
+        <v>0.5609756097560976</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.909090909090909</v>
+        <v>0.3647058823529412</v>
       </c>
       <c r="R16" t="n">
-        <v>0.1746031746031746</v>
+        <v>0.2317073170731707</v>
       </c>
       <c r="S16" t="n">
-        <v>4.888600662028175</v>
+        <v>5.504148590237152</v>
       </c>
       <c r="T16" t="n">
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>0.9196182309009308</v>
+        <v>0.9717090448049768</v>
       </c>
     </row>
     <row r="17">
@@ -1582,61 +1582,61 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>751908</v>
+        <v>282909</v>
       </c>
       <c r="D17" t="n">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="E17" t="n">
-        <v>22</v>
+        <v>52</v>
       </c>
       <c r="F17" t="n">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="G17" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>24</v>
+        <v>96</v>
       </c>
       <c r="I17" t="n">
-        <v>18</v>
+        <v>67</v>
       </c>
       <c r="J17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L17" t="n">
         <v>2</v>
       </c>
       <c r="M17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P17" t="n">
-        <v>1.272727272727273</v>
+        <v>0.9423076923076923</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.4235294117647059</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.333333333333333</v>
+        <v>1.432835820895522</v>
       </c>
       <c r="S17" t="n">
-        <v>5.87616528315911</v>
+        <v>5.451648298705005</v>
       </c>
       <c r="T17" t="n">
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>0.9562183254614089</v>
+        <v>0.9763300720344047</v>
       </c>
     </row>
     <row r="18">
@@ -1651,34 +1651,34 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>926310</v>
+        <v>785435</v>
       </c>
       <c r="D18" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E18" t="n">
-        <v>95</v>
+        <v>20</v>
       </c>
       <c r="F18" t="n">
-        <v>66</v>
+        <v>17</v>
       </c>
       <c r="G18" t="n">
-        <v>45</v>
+        <v>88</v>
       </c>
       <c r="H18" t="n">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="I18" t="n">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="J18" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="K18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M18" t="n">
         <v>1</v>
@@ -1687,25 +1687,25 @@
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>0.9473684210526315</v>
+        <v>4.45</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.466666666666667</v>
+        <v>0.1931818181818182</v>
       </c>
       <c r="R18" t="n">
-        <v>4</v>
+        <v>1.051282051282051</v>
       </c>
       <c r="S18" t="n">
-        <v>5.966756821355638</v>
+        <v>5.895110803024343</v>
       </c>
       <c r="T18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>0.9881868983431464</v>
+        <v>0.3899697590712324</v>
       </c>
     </row>
     <row r="19">
@@ -1720,28 +1720,28 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>317016</v>
+        <v>496134</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E19" t="n">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="F19" t="n">
-        <v>12</v>
+        <v>92</v>
       </c>
       <c r="G19" t="n">
+        <v>5</v>
+      </c>
+      <c r="H19" t="n">
+        <v>92</v>
+      </c>
+      <c r="I19" t="n">
         <v>26</v>
       </c>
-      <c r="H19" t="n">
-        <v>64</v>
-      </c>
-      <c r="I19" t="n">
-        <v>42</v>
-      </c>
       <c r="J19" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K19" t="n">
         <v>1</v>
@@ -1750,31 +1750,31 @@
         <v>2</v>
       </c>
       <c r="M19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>0.2967032967032967</v>
+        <v>1.55</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.4615384615384616</v>
+        <v>18.4</v>
       </c>
       <c r="R19" t="n">
-        <v>1.523809523809524</v>
+        <v>3.538461538461538</v>
       </c>
       <c r="S19" t="n">
-        <v>5.501082551833626</v>
+        <v>5.695599865558053</v>
       </c>
       <c r="T19" t="n">
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>0.8654075085728185</v>
+        <v>0.9935217086701253</v>
       </c>
     </row>
     <row r="20">
@@ -1789,31 +1789,31 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>256063</v>
+        <v>228068</v>
       </c>
       <c r="D20" t="n">
-        <v>43</v>
+        <v>76</v>
       </c>
       <c r="E20" t="n">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="F20" t="n">
-        <v>1</v>
+        <v>69</v>
       </c>
       <c r="G20" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="H20" t="n">
-        <v>99</v>
+        <v>17</v>
       </c>
       <c r="I20" t="n">
-        <v>28</v>
+        <v>77</v>
       </c>
       <c r="J20" t="n">
         <v>3</v>
       </c>
       <c r="K20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -1822,28 +1822,28 @@
         <v>1</v>
       </c>
       <c r="N20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P20" t="n">
-        <v>0.86</v>
+        <v>1.055555555555556</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.25</v>
+        <v>2.464285714285714</v>
       </c>
       <c r="R20" t="n">
-        <v>3.535714285714286</v>
+        <v>0.2207792207792208</v>
       </c>
       <c r="S20" t="n">
-        <v>5.408348525362884</v>
+        <v>5.358066258341633</v>
       </c>
       <c r="T20" t="n">
         <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>0.964014172005751</v>
+        <v>0.9639976153380886</v>
       </c>
     </row>
     <row r="21">
@@ -1858,61 +1858,61 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>4567</v>
+        <v>67484</v>
       </c>
       <c r="D21" t="n">
-        <v>61</v>
+        <v>24</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="F21" t="n">
-        <v>71</v>
+        <v>37</v>
       </c>
       <c r="G21" t="n">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="H21" t="n">
-        <v>13</v>
+        <v>57</v>
       </c>
       <c r="I21" t="n">
-        <v>89</v>
+        <v>1</v>
       </c>
       <c r="J21" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K21" t="n">
         <v>2</v>
       </c>
       <c r="L21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>0.3692307692307693</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.8658536585365854</v>
+        <v>0.5362318840579711</v>
       </c>
       <c r="R21" t="n">
-        <v>0.1460674157303371</v>
+        <v>57</v>
       </c>
       <c r="S21" t="n">
-        <v>3.659726095237791</v>
+        <v>4.829207252221248</v>
       </c>
       <c r="T21" t="n">
         <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>0.8214424750868838</v>
+        <v>0.9407365214293919</v>
       </c>
     </row>
     <row r="22">
@@ -1927,61 +1927,61 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>256210</v>
+        <v>546914</v>
       </c>
       <c r="D22" t="n">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="E22" t="n">
-        <v>95</v>
+        <v>40</v>
       </c>
       <c r="F22" t="n">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="G22" t="n">
-        <v>89</v>
+        <v>38</v>
       </c>
       <c r="H22" t="n">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="I22" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="J22" t="n">
         <v>4</v>
       </c>
       <c r="K22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L22" t="n">
         <v>1</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P22" t="n">
-        <v>0.7684210526315789</v>
+        <v>2.3</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.8202247191011236</v>
+        <v>2.473684210526316</v>
       </c>
       <c r="R22" t="n">
-        <v>0.625</v>
+        <v>0.9444444444444444</v>
       </c>
       <c r="S22" t="n">
-        <v>5.408597771531806</v>
+        <v>5.737919834743982</v>
       </c>
       <c r="T22" t="n">
         <v>1</v>
       </c>
       <c r="U22" t="n">
-        <v>0.993287142043614</v>
+        <v>0.9405287007603736</v>
       </c>
     </row>
     <row r="23">
@@ -1996,31 +1996,31 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>971153</v>
+        <v>136669</v>
       </c>
       <c r="D23" t="n">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="E23" t="n">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="F23" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="G23" t="n">
-        <v>2</v>
+        <v>42</v>
       </c>
       <c r="H23" t="n">
-        <v>88</v>
+        <v>14</v>
       </c>
       <c r="I23" t="n">
-        <v>5</v>
+        <v>87</v>
       </c>
       <c r="J23" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="K23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -2035,22 +2035,22 @@
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>1.094117647058824</v>
+        <v>1.260869565217391</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.5</v>
+        <v>0.5952380952380952</v>
       </c>
       <c r="R23" t="n">
-        <v>17.6</v>
+        <v>0.1609195402298851</v>
       </c>
       <c r="S23" t="n">
-        <v>5.987288103282983</v>
+        <v>5.135673194419237</v>
       </c>
       <c r="T23" t="n">
         <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>0.8660608820376384</v>
+        <v>0.9783659591055488</v>
       </c>
     </row>
     <row r="24">
@@ -2065,31 +2065,31 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>638111</v>
+        <v>936091</v>
       </c>
       <c r="D24" t="n">
-        <v>23</v>
+        <v>73</v>
       </c>
       <c r="E24" t="n">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="F24" t="n">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="G24" t="n">
-        <v>96</v>
+        <v>5</v>
       </c>
       <c r="H24" t="n">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="I24" t="n">
-        <v>74</v>
+        <v>36</v>
       </c>
       <c r="J24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L24" t="n">
         <v>1</v>
@@ -2104,22 +2104,22 @@
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>0.4791666666666667</v>
+        <v>2.147058823529412</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.03125</v>
+        <v>8</v>
       </c>
       <c r="R24" t="n">
-        <v>1.283783783783784</v>
+        <v>2.472222222222222</v>
       </c>
       <c r="S24" t="n">
-        <v>5.804896911813709</v>
+        <v>5.971318533704835</v>
       </c>
       <c r="T24" t="n">
         <v>1</v>
       </c>
       <c r="U24" t="n">
-        <v>0.9499516912365854</v>
+        <v>0.9295424410829943</v>
       </c>
     </row>
     <row r="25">
@@ -2134,28 +2134,28 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>396318</v>
+        <v>207857</v>
       </c>
       <c r="D25" t="n">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="E25" t="n">
-        <v>81</v>
+        <v>2</v>
       </c>
       <c r="F25" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="G25" t="n">
-        <v>2</v>
+        <v>90</v>
       </c>
       <c r="H25" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="I25" t="n">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="J25" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K25" t="n">
         <v>2</v>
@@ -2164,7 +2164,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
@@ -2173,22 +2173,22 @@
         <v>1</v>
       </c>
       <c r="P25" t="n">
-        <v>0.4320987654320987</v>
+        <v>37.5</v>
       </c>
       <c r="Q25" t="n">
-        <v>20</v>
+        <v>0.2555555555555555</v>
       </c>
       <c r="R25" t="n">
-        <v>0.0119047619047619</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="S25" t="n">
-        <v>5.598044893422651</v>
+        <v>5.317766744209057</v>
       </c>
       <c r="T25" t="n">
         <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>0.9400729637196262</v>
+        <v>0.7636936207636851</v>
       </c>
     </row>
     <row r="26">
@@ -2203,61 +2203,61 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>719598</v>
+        <v>905277</v>
       </c>
       <c r="D26" t="n">
-        <v>15</v>
+        <v>81</v>
       </c>
       <c r="E26" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>28</v>
+        <v>58</v>
       </c>
       <c r="G26" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="H26" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="I26" t="n">
-        <v>37</v>
+        <v>79</v>
       </c>
       <c r="J26" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="K26" t="n">
         <v>2</v>
       </c>
       <c r="L26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
         <v>1</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P26" t="n">
-        <v>0.1612903225806452</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.725</v>
       </c>
       <c r="R26" t="n">
-        <v>0.02702702702702703</v>
+        <v>0.2784810126582278</v>
       </c>
       <c r="S26" t="n">
-        <v>5.857090551151024</v>
+        <v>5.956781966305878</v>
       </c>
       <c r="T26" t="n">
         <v>1</v>
       </c>
       <c r="U26" t="n">
-        <v>0.8243604857036674</v>
+        <v>0.8329489247199406</v>
       </c>
     </row>
     <row r="27">
@@ -2272,61 +2272,61 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>697288</v>
+        <v>471242</v>
       </c>
       <c r="D27" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="E27" t="n">
-        <v>66</v>
+        <v>20</v>
       </c>
       <c r="F27" t="n">
-        <v>87</v>
+        <v>48</v>
       </c>
       <c r="G27" t="n">
+        <v>47</v>
+      </c>
+      <c r="H27" t="n">
+        <v>34</v>
+      </c>
+      <c r="I27" t="n">
         <v>4</v>
-      </c>
-      <c r="H27" t="n">
-        <v>37</v>
-      </c>
-      <c r="I27" t="n">
-        <v>72</v>
       </c>
       <c r="J27" t="n">
         <v>6</v>
       </c>
       <c r="K27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>0.4242424242424243</v>
+        <v>1.8</v>
       </c>
       <c r="Q27" t="n">
-        <v>21.75</v>
+        <v>1.021276595744681</v>
       </c>
       <c r="R27" t="n">
-        <v>0.5138888888888888</v>
+        <v>8.5</v>
       </c>
       <c r="S27" t="n">
-        <v>5.843412814097817</v>
+        <v>5.673244912107319</v>
       </c>
       <c r="T27" t="n">
         <v>1</v>
       </c>
       <c r="U27" t="n">
-        <v>0.9424479098938495</v>
+        <v>0.8972625945390422</v>
       </c>
     </row>
     <row r="28">
@@ -2341,61 +2341,61 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>546029</v>
+        <v>164648</v>
       </c>
       <c r="D28" t="n">
-        <v>92</v>
+        <v>67</v>
       </c>
       <c r="E28" t="n">
-        <v>75</v>
+        <v>27</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="G28" t="n">
-        <v>85</v>
+        <v>35</v>
       </c>
       <c r="H28" t="n">
-        <v>91</v>
+        <v>50</v>
       </c>
       <c r="I28" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="J28" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K28" t="n">
         <v>1</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>1</v>
       </c>
       <c r="P28" t="n">
-        <v>1.226666666666667</v>
+        <v>2.481481481481481</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>2.057142857142857</v>
       </c>
       <c r="R28" t="n">
-        <v>2.676470588235294</v>
+        <v>1.282051282051282</v>
       </c>
       <c r="S28" t="n">
-        <v>5.737216504383373</v>
+        <v>5.216559097357063</v>
       </c>
       <c r="T28" t="n">
         <v>1</v>
       </c>
       <c r="U28" t="n">
-        <v>0.9857503810939514</v>
+        <v>0.8637924310417309</v>
       </c>
     </row>
     <row r="29">
@@ -2410,61 +2410,61 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>995266</v>
+        <v>349593</v>
       </c>
       <c r="D29" t="n">
-        <v>47</v>
+        <v>12</v>
       </c>
       <c r="E29" t="n">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="F29" t="n">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="G29" t="n">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="H29" t="n">
-        <v>78</v>
+        <v>95</v>
       </c>
       <c r="I29" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="J29" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="K29" t="n">
         <v>2</v>
       </c>
       <c r="L29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>1.044444444444445</v>
+        <v>0.1481481481481481</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.375</v>
+        <v>1.326530612244898</v>
       </c>
       <c r="R29" t="n">
-        <v>0.7878787878787878</v>
+        <v>0.979381443298969</v>
       </c>
       <c r="S29" t="n">
-        <v>5.997939604435627</v>
+        <v>5.543563970331781</v>
       </c>
       <c r="T29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>0.9891771895533269</v>
+        <v>0.3911108382718969</v>
       </c>
     </row>
     <row r="30">
@@ -2479,61 +2479,61 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>639526</v>
+        <v>414125</v>
       </c>
       <c r="D30" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="E30" t="n">
-        <v>73</v>
+        <v>5</v>
       </c>
       <c r="F30" t="n">
-        <v>90</v>
+        <v>33</v>
       </c>
       <c r="G30" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="H30" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="I30" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="J30" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P30" t="n">
-        <v>0.726027397260274</v>
+        <v>11.4</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.8</v>
+        <v>0.559322033898305</v>
       </c>
       <c r="R30" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="S30" t="n">
-        <v>5.805858884551156</v>
+        <v>5.617132497592601</v>
       </c>
       <c r="T30" t="n">
         <v>1</v>
       </c>
       <c r="U30" t="n">
-        <v>0.9874476179190552</v>
+        <v>0.8249437654519776</v>
       </c>
     </row>
     <row r="31">
@@ -2548,61 +2548,61 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>556083</v>
+        <v>560206</v>
       </c>
       <c r="D31" t="n">
-        <v>82</v>
+        <v>56</v>
       </c>
       <c r="E31" t="n">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="F31" t="n">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="G31" t="n">
-        <v>66</v>
+        <v>23</v>
       </c>
       <c r="H31" t="n">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="I31" t="n">
-        <v>1</v>
+        <v>91</v>
       </c>
       <c r="J31" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P31" t="n">
-        <v>1.064935064935065</v>
+        <v>0.7887323943661971</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.454545454545455</v>
+        <v>3.304347826086957</v>
       </c>
       <c r="R31" t="n">
-        <v>64</v>
+        <v>0.6483516483516484</v>
       </c>
       <c r="S31" t="n">
-        <v>5.745140399461587</v>
+        <v>5.748348531196546</v>
       </c>
       <c r="T31" t="n">
         <v>1</v>
       </c>
       <c r="U31" t="n">
-        <v>0.9927285672515819</v>
+        <v>0.9920257150636157</v>
       </c>
     </row>
     <row r="32">
@@ -2617,61 +2617,61 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>131789</v>
+        <v>794795</v>
       </c>
       <c r="D32" t="n">
-        <v>2</v>
+        <v>82</v>
       </c>
       <c r="E32" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>22</v>
+        <v>73</v>
       </c>
       <c r="G32" t="n">
-        <v>26</v>
+        <v>57</v>
       </c>
       <c r="H32" t="n">
-        <v>26</v>
+        <v>74</v>
       </c>
       <c r="I32" t="n">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="J32" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K32" t="n">
         <v>1</v>
       </c>
       <c r="L32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.8461538461538461</v>
+        <v>1.280701754385965</v>
       </c>
       <c r="R32" t="n">
-        <v>0.2888888888888889</v>
+        <v>0.7628865979381443</v>
       </c>
       <c r="S32" t="n">
-        <v>5.119882457984983</v>
+        <v>5.900255672752952</v>
       </c>
       <c r="T32" t="n">
         <v>1</v>
       </c>
       <c r="U32" t="n">
-        <v>0.6566255051831551</v>
+        <v>0.872883038035427</v>
       </c>
     </row>
     <row r="33">
@@ -2686,61 +2686,61 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>335581</v>
+        <v>805619</v>
       </c>
       <c r="D33" t="n">
-        <v>55</v>
+        <v>79</v>
       </c>
       <c r="E33" t="n">
-        <v>92</v>
+        <v>2</v>
       </c>
       <c r="F33" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="G33" t="n">
+        <v>90</v>
+      </c>
+      <c r="H33" t="n">
         <v>29</v>
       </c>
-      <c r="H33" t="n">
-        <v>79</v>
-      </c>
       <c r="I33" t="n">
-        <v>88</v>
+        <v>35</v>
       </c>
       <c r="J33" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>0.5978260869565217</v>
+        <v>39.5</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.8275862068965517</v>
+        <v>0.4</v>
       </c>
       <c r="R33" t="n">
-        <v>0.8977272727272727</v>
+        <v>0.8285714285714286</v>
       </c>
       <c r="S33" t="n">
-        <v>5.525798658025782</v>
+        <v>5.906130239300553</v>
       </c>
       <c r="T33" t="n">
         <v>1</v>
       </c>
       <c r="U33" t="n">
-        <v>0.9754333808678405</v>
+        <v>0.8123684161527198</v>
       </c>
     </row>
     <row r="34">
@@ -2755,61 +2755,61 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>917923</v>
+        <v>172723</v>
       </c>
       <c r="D34" t="n">
-        <v>11</v>
+        <v>99</v>
       </c>
       <c r="E34" t="n">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="F34" t="n">
-        <v>56</v>
+        <v>83</v>
       </c>
       <c r="G34" t="n">
-        <v>59</v>
+        <v>10</v>
       </c>
       <c r="H34" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="I34" t="n">
-        <v>15</v>
+        <v>63</v>
       </c>
       <c r="J34" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K34" t="n">
         <v>2</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M34" t="n">
         <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P34" t="n">
-        <v>0.1896551724137931</v>
+        <v>1.375</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.9491525423728814</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="R34" t="n">
-        <v>3.6</v>
+        <v>0.9523809523809523</v>
       </c>
       <c r="S34" t="n">
-        <v>5.962806725049851</v>
+        <v>5.237352686979095</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U34" t="n">
-        <v>0.4986984928300782</v>
+        <v>0.9728566337788493</v>
       </c>
     </row>
     <row r="35">
@@ -2824,37 +2824,37 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>540495</v>
+        <v>925771</v>
       </c>
       <c r="D35" t="n">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="E35" t="n">
-        <v>92</v>
+        <v>14</v>
       </c>
       <c r="F35" t="n">
-        <v>97</v>
+        <v>3</v>
       </c>
       <c r="G35" t="n">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="H35" t="n">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="I35" t="n">
-        <v>16</v>
+        <v>49</v>
       </c>
       <c r="J35" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N35" t="n">
         <v>1</v>
@@ -2863,22 +2863,22 @@
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>0.3369565217391304</v>
+        <v>1.285714285714286</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.515625</v>
+        <v>0.09375</v>
       </c>
       <c r="R35" t="n">
-        <v>1.5</v>
+        <v>1.122448979591837</v>
       </c>
       <c r="S35" t="n">
-        <v>5.732792484257219</v>
+        <v>5.966504041396689</v>
       </c>
       <c r="T35" t="n">
         <v>1</v>
       </c>
       <c r="U35" t="n">
-        <v>0.8609857584412005</v>
+        <v>0.719131062754619</v>
       </c>
     </row>
     <row r="36">
@@ -2893,31 +2893,31 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>456554</v>
+        <v>924553</v>
       </c>
       <c r="D36" t="n">
-        <v>32</v>
+        <v>92</v>
       </c>
       <c r="E36" t="n">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="F36" t="n">
-        <v>10</v>
+        <v>69</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="H36" t="n">
-        <v>77</v>
+        <v>14</v>
       </c>
       <c r="I36" t="n">
-        <v>59</v>
+        <v>15</v>
       </c>
       <c r="J36" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="K36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L36" t="n">
         <v>1</v>
@@ -2926,28 +2926,28 @@
         <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P36" t="n">
-        <v>0.6808510638297872</v>
+        <v>2.24390243902439</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>2.653846153846154</v>
       </c>
       <c r="R36" t="n">
-        <v>1.305084745762712</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="S36" t="n">
-        <v>5.659493103354858</v>
+        <v>5.965932281873923</v>
       </c>
       <c r="T36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>0.9704541670127669</v>
+        <v>0.3914535225305705</v>
       </c>
     </row>
     <row r="37">
@@ -2962,61 +2962,61 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>896892</v>
+        <v>604737</v>
       </c>
       <c r="D37" t="n">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="E37" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="F37" t="n">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="G37" t="n">
-        <v>98</v>
+        <v>63</v>
       </c>
       <c r="H37" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="I37" t="n">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="J37" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>3.208333333333333</v>
+        <v>18.5</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.4693877551020408</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="R37" t="n">
-        <v>0.4935064935064935</v>
+        <v>0.4666666666666667</v>
       </c>
       <c r="S37" t="n">
-        <v>5.952740634480684</v>
+        <v>5.781567259281971</v>
       </c>
       <c r="T37" t="n">
         <v>1</v>
       </c>
       <c r="U37" t="n">
-        <v>0.8635499308685192</v>
+        <v>0.7872080613025997</v>
       </c>
     </row>
     <row r="38">
@@ -3031,61 +3031,61 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>250146</v>
+        <v>16879</v>
       </c>
       <c r="D38" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>47</v>
+        <v>10</v>
       </c>
       <c r="F38" t="n">
-        <v>59</v>
+        <v>90</v>
       </c>
       <c r="G38" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="H38" t="n">
-        <v>59</v>
+        <v>20</v>
       </c>
       <c r="I38" t="n">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="J38" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="K38" t="n">
         <v>2</v>
       </c>
       <c r="L38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>1.829787234042553</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.685714285714286</v>
+        <v>2.903225806451613</v>
       </c>
       <c r="R38" t="n">
-        <v>19.66666666666667</v>
+        <v>0.7407407407407407</v>
       </c>
       <c r="S38" t="n">
-        <v>5.398195298779458</v>
+        <v>4.227372442289636</v>
       </c>
       <c r="T38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>0.9797659765227429</v>
+        <v>0.1053767714674922</v>
       </c>
     </row>
     <row r="39">
@@ -3100,28 +3100,28 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>226293</v>
+        <v>971624</v>
       </c>
       <c r="D39" t="n">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="E39" t="n">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="F39" t="n">
-        <v>98</v>
+        <v>6</v>
       </c>
       <c r="G39" t="n">
-        <v>10</v>
+        <v>67</v>
       </c>
       <c r="H39" t="n">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="I39" t="n">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="J39" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K39" t="n">
         <v>2</v>
@@ -3133,28 +3133,28 @@
         <v>1</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>0.1754385964912281</v>
+        <v>1.235294117647059</v>
       </c>
       <c r="Q39" t="n">
-        <v>9.800000000000001</v>
+        <v>0.08955223880597014</v>
       </c>
       <c r="R39" t="n">
-        <v>1.03448275862069</v>
+        <v>1.888888888888889</v>
       </c>
       <c r="S39" t="n">
-        <v>5.354673039145025</v>
+        <v>5.987498680713544</v>
       </c>
       <c r="T39" t="n">
         <v>1</v>
       </c>
       <c r="U39" t="n">
-        <v>0.7895699739296063</v>
+        <v>0.8426631685820092</v>
       </c>
     </row>
     <row r="40">
@@ -3169,31 +3169,31 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>403963</v>
+        <v>970184</v>
       </c>
       <c r="D40" t="n">
-        <v>58</v>
+        <v>23</v>
       </c>
       <c r="E40" t="n">
-        <v>90</v>
+        <v>6</v>
       </c>
       <c r="F40" t="n">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="G40" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="H40" t="n">
-        <v>26</v>
+        <v>83</v>
       </c>
       <c r="I40" t="n">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="J40" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L40" t="n">
         <v>1</v>
@@ -3205,25 +3205,25 @@
         <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>0.6444444444444445</v>
+        <v>3.833333333333333</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.894736842105263</v>
+        <v>1.964285714285714</v>
       </c>
       <c r="R40" t="n">
-        <v>0.3132530120481928</v>
+        <v>1.202898550724638</v>
       </c>
       <c r="S40" t="n">
-        <v>5.606342663877979</v>
+        <v>5.986854555728524</v>
       </c>
       <c r="T40" t="n">
         <v>1</v>
       </c>
       <c r="U40" t="n">
-        <v>0.8379875689394575</v>
+        <v>0.8299759002028385</v>
       </c>
     </row>
     <row r="41">
@@ -3238,34 +3238,34 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>661123</v>
+        <v>110282</v>
       </c>
       <c r="D41" t="n">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="E41" t="n">
-        <v>15</v>
+        <v>99</v>
       </c>
       <c r="F41" t="n">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="G41" t="n">
-        <v>1</v>
+        <v>76</v>
       </c>
       <c r="H41" t="n">
-        <v>32</v>
+        <v>81</v>
       </c>
       <c r="I41" t="n">
-        <v>14</v>
+        <v>65</v>
       </c>
       <c r="J41" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="K41" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
         <v>0</v>
@@ -3274,25 +3274,25 @@
         <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P41" t="n">
-        <v>6.066666666666666</v>
+        <v>0.8282828282828283</v>
       </c>
       <c r="Q41" t="n">
-        <v>90</v>
+        <v>0.02631578947368421</v>
       </c>
       <c r="R41" t="n">
-        <v>2.285714285714286</v>
+        <v>1.246153846153846</v>
       </c>
       <c r="S41" t="n">
-        <v>5.820282923124322</v>
+        <v>5.042508571595184</v>
       </c>
       <c r="T41" t="n">
         <v>1</v>
       </c>
       <c r="U41" t="n">
-        <v>0.8673368477218496</v>
+        <v>0.7991686637880432</v>
       </c>
     </row>
     <row r="42">
@@ -3307,37 +3307,37 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>233634</v>
+        <v>588420</v>
       </c>
       <c r="D42" t="n">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="E42" t="n">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="F42" t="n">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="G42" t="n">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="H42" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="I42" t="n">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="J42" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
         <v>0</v>
@@ -3346,22 +3346,22 @@
         <v>1</v>
       </c>
       <c r="P42" t="n">
-        <v>1.352941176470588</v>
+        <v>17</v>
       </c>
       <c r="Q42" t="n">
-        <v>1.066666666666667</v>
+        <v>1</v>
       </c>
       <c r="R42" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.5</v>
       </c>
       <c r="S42" t="n">
-        <v>5.368537903372976</v>
+        <v>5.769688163751914</v>
       </c>
       <c r="T42" t="n">
         <v>1</v>
       </c>
       <c r="U42" t="n">
-        <v>0.9319374709479427</v>
+        <v>0.7159250312637587</v>
       </c>
     </row>
     <row r="43">
@@ -3376,61 +3376,61 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>181984</v>
+        <v>591832</v>
       </c>
       <c r="D43" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>66</v>
+        <v>96</v>
       </c>
       <c r="F43" t="n">
-        <v>99</v>
+        <v>1</v>
       </c>
       <c r="G43" t="n">
-        <v>54</v>
+        <v>97</v>
       </c>
       <c r="H43" t="n">
-        <v>96</v>
+        <v>35</v>
       </c>
       <c r="I43" t="n">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="J43" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P43" t="n">
-        <v>0.2727272727272727</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.833333333333333</v>
+        <v>0.01030927835051546</v>
       </c>
       <c r="R43" t="n">
-        <v>1.432835820895522</v>
+        <v>0.660377358490566</v>
       </c>
       <c r="S43" t="n">
-        <v>5.260035593008731</v>
+        <v>5.772199177313858</v>
       </c>
       <c r="T43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>0.8915674908657261</v>
+        <v>0.3139522146548168</v>
       </c>
     </row>
     <row r="44">
@@ -3445,37 +3445,37 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>284589</v>
+        <v>578792</v>
       </c>
       <c r="D44" t="n">
-        <v>99</v>
+        <v>37</v>
       </c>
       <c r="E44" t="n">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="F44" t="n">
-        <v>75</v>
+        <v>34</v>
       </c>
       <c r="G44" t="n">
-        <v>97</v>
+        <v>40</v>
       </c>
       <c r="H44" t="n">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="I44" t="n">
-        <v>38</v>
+        <v>78</v>
       </c>
       <c r="J44" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N44" t="n">
         <v>0</v>
@@ -3484,22 +3484,22 @@
         <v>1</v>
       </c>
       <c r="P44" t="n">
-        <v>1.941176470588235</v>
+        <v>0.9487179487179487</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.7731958762886598</v>
+        <v>0.85</v>
       </c>
       <c r="R44" t="n">
-        <v>0.6842105263157895</v>
+        <v>0.5769230769230769</v>
       </c>
       <c r="S44" t="n">
-        <v>5.454219635660001</v>
+        <v>5.762523270063177</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U44" t="n">
-        <v>0.3785089071026237</v>
+        <v>0.9920169285983285</v>
       </c>
     </row>
     <row r="45">
@@ -3514,37 +3514,37 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>243134</v>
+        <v>723461</v>
       </c>
       <c r="D45" t="n">
-        <v>98</v>
+        <v>47</v>
       </c>
       <c r="E45" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="F45" t="n">
-        <v>90</v>
+        <v>3</v>
       </c>
       <c r="G45" t="n">
-        <v>62</v>
+        <v>99</v>
       </c>
       <c r="H45" t="n">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="I45" t="n">
-        <v>97</v>
+        <v>56</v>
       </c>
       <c r="J45" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K45" t="n">
         <v>1</v>
       </c>
       <c r="L45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
         <v>1</v>
@@ -3553,22 +3553,22 @@
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>49</v>
+        <v>1.175</v>
       </c>
       <c r="Q45" t="n">
-        <v>1.451612903225806</v>
+        <v>0.0303030303030303</v>
       </c>
       <c r="R45" t="n">
-        <v>0.4742268041237113</v>
+        <v>1.339285714285714</v>
       </c>
       <c r="S45" t="n">
-        <v>5.385847481314539</v>
+        <v>5.859415724641343</v>
       </c>
       <c r="T45" t="n">
         <v>1</v>
       </c>
       <c r="U45" t="n">
-        <v>0.7536221298932514</v>
+        <v>0.8559077422846684</v>
       </c>
     </row>
     <row r="46">
@@ -3583,61 +3583,61 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>351572</v>
+        <v>664473</v>
       </c>
       <c r="D46" t="n">
-        <v>88</v>
+        <v>48</v>
       </c>
       <c r="E46" t="n">
+        <v>65</v>
+      </c>
+      <c r="F46" t="n">
+        <v>20</v>
+      </c>
+      <c r="G46" t="n">
+        <v>4</v>
+      </c>
+      <c r="H46" t="n">
+        <v>51</v>
+      </c>
+      <c r="I46" t="n">
         <v>17</v>
       </c>
-      <c r="F46" t="n">
-        <v>49</v>
-      </c>
-      <c r="G46" t="n">
-        <v>57</v>
-      </c>
-      <c r="H46" t="n">
-        <v>28</v>
-      </c>
-      <c r="I46" t="n">
-        <v>30</v>
-      </c>
       <c r="J46" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K46" t="n">
         <v>2</v>
       </c>
       <c r="L46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
         <v>1</v>
       </c>
       <c r="N46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
         <v>1</v>
       </c>
       <c r="P46" t="n">
-        <v>5.176470588235294</v>
+        <v>0.7384615384615385</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.8596491228070176</v>
+        <v>5</v>
       </c>
       <c r="R46" t="n">
-        <v>0.9333333333333333</v>
+        <v>3</v>
       </c>
       <c r="S46" t="n">
-        <v>5.546015514862306</v>
+        <v>5.822477992235198</v>
       </c>
       <c r="T46" t="n">
         <v>1</v>
       </c>
       <c r="U46" t="n">
-        <v>0.8431890420695436</v>
+        <v>0.984993189066615</v>
       </c>
     </row>
     <row r="47">
@@ -3652,61 +3652,61 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>141709</v>
+        <v>956102</v>
       </c>
       <c r="D47" t="n">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="E47" t="n">
-        <v>68</v>
+        <v>31</v>
       </c>
       <c r="F47" t="n">
-        <v>72</v>
+        <v>12</v>
       </c>
       <c r="G47" t="n">
-        <v>94</v>
+        <v>45</v>
       </c>
       <c r="H47" t="n">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="I47" t="n">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="J47" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="K47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
         <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P47" t="n">
-        <v>0.3676470588235294</v>
+        <v>1.548387096774194</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.7659574468085106</v>
+        <v>0.2666666666666667</v>
       </c>
       <c r="R47" t="n">
-        <v>2.153846153846154</v>
+        <v>1.36734693877551</v>
       </c>
       <c r="S47" t="n">
-        <v>5.151400498035618</v>
+        <v>5.980504680897507</v>
       </c>
       <c r="T47" t="n">
         <v>1</v>
       </c>
       <c r="U47" t="n">
-        <v>0.9297239085637201</v>
+        <v>0.9689940431491633</v>
       </c>
     </row>
     <row r="48">
@@ -3721,61 +3721,61 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>600511</v>
+        <v>569749</v>
       </c>
       <c r="D48" t="n">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="E48" t="n">
-        <v>59</v>
+        <v>96</v>
       </c>
       <c r="F48" t="n">
-        <v>85</v>
+        <v>22</v>
       </c>
       <c r="G48" t="n">
-        <v>95</v>
+        <v>3</v>
       </c>
       <c r="H48" t="n">
-        <v>19</v>
+        <v>83</v>
       </c>
       <c r="I48" t="n">
-        <v>21</v>
+        <v>97</v>
       </c>
       <c r="J48" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>1</v>
       </c>
       <c r="P48" t="n">
-        <v>1.423728813559322</v>
+        <v>0.9895833333333334</v>
       </c>
       <c r="Q48" t="n">
-        <v>0.8947368421052632</v>
+        <v>7.333333333333333</v>
       </c>
       <c r="R48" t="n">
-        <v>0.9047619047619048</v>
+        <v>0.8556701030927835</v>
       </c>
       <c r="S48" t="n">
-        <v>5.778521690309635</v>
+        <v>5.755684333852413</v>
       </c>
       <c r="T48" t="n">
         <v>1</v>
       </c>
       <c r="U48" t="n">
-        <v>0.9867532093074256</v>
+        <v>0.9903788506404814</v>
       </c>
     </row>
     <row r="49">
@@ -3790,37 +3790,37 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>735982</v>
+        <v>873025</v>
       </c>
       <c r="D49" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="E49" t="n">
-        <v>7</v>
+        <v>68</v>
       </c>
       <c r="F49" t="n">
-        <v>75</v>
+        <v>20</v>
       </c>
       <c r="G49" t="n">
-        <v>84</v>
+        <v>56</v>
       </c>
       <c r="H49" t="n">
+        <v>5</v>
+      </c>
+      <c r="I49" t="n">
         <v>13</v>
       </c>
-      <c r="I49" t="n">
-        <v>22</v>
-      </c>
       <c r="J49" t="n">
         <v>2</v>
       </c>
       <c r="K49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N49" t="n">
         <v>0</v>
@@ -3829,22 +3829,22 @@
         <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>2.571428571428572</v>
+        <v>0.4264705882352941</v>
       </c>
       <c r="Q49" t="n">
-        <v>0.8928571428571429</v>
+        <v>0.3571428571428572</v>
       </c>
       <c r="R49" t="n">
-        <v>0.5909090909090909</v>
+        <v>0.3846153846153846</v>
       </c>
       <c r="S49" t="n">
-        <v>5.866867782963234</v>
+        <v>5.941027177827433</v>
       </c>
       <c r="T49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U49" t="n">
-        <v>0.136499477818059</v>
+        <v>0.7068115305210871</v>
       </c>
     </row>
     <row r="50">
@@ -3859,28 +3859,28 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>24634</v>
+        <v>484758</v>
       </c>
       <c r="D50" t="n">
-        <v>39</v>
+        <v>71</v>
       </c>
       <c r="E50" t="n">
-        <v>71</v>
+        <v>25</v>
       </c>
       <c r="F50" t="n">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="G50" t="n">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="H50" t="n">
-        <v>13</v>
+        <v>77</v>
       </c>
       <c r="I50" t="n">
-        <v>94</v>
+        <v>22</v>
       </c>
       <c r="J50" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K50" t="n">
         <v>1</v>
@@ -3895,25 +3895,25 @@
         <v>1</v>
       </c>
       <c r="O50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>0.5492957746478874</v>
+        <v>2.84</v>
       </c>
       <c r="Q50" t="n">
-        <v>0.4305555555555556</v>
+        <v>0.8</v>
       </c>
       <c r="R50" t="n">
-        <v>0.1382978723404255</v>
+        <v>3.5</v>
       </c>
       <c r="S50" t="n">
-        <v>4.391552566610928</v>
+        <v>5.685525880905056</v>
       </c>
       <c r="T50" t="n">
         <v>1</v>
       </c>
       <c r="U50" t="n">
-        <v>0.9772976948510802</v>
+        <v>0.8994249880338175</v>
       </c>
     </row>
     <row r="51">
@@ -3928,34 +3928,34 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>633815</v>
+        <v>881207</v>
       </c>
       <c r="D51" t="n">
-        <v>88</v>
+        <v>3</v>
       </c>
       <c r="E51" t="n">
-        <v>72</v>
+        <v>5</v>
       </c>
       <c r="F51" t="n">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="G51" t="n">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="H51" t="n">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="I51" t="n">
-        <v>84</v>
+        <v>3</v>
       </c>
       <c r="J51" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M51" t="n">
         <v>0</v>
@@ -3964,25 +3964,25 @@
         <v>1</v>
       </c>
       <c r="O51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>1.222222222222222</v>
+        <v>0.6</v>
       </c>
       <c r="Q51" t="n">
-        <v>0.3766233766233766</v>
+        <v>0.06315789473684211</v>
       </c>
       <c r="R51" t="n">
-        <v>1.035714285714286</v>
+        <v>24.66666666666667</v>
       </c>
       <c r="S51" t="n">
-        <v>5.801963198287547</v>
+        <v>5.945078431216002</v>
       </c>
       <c r="T51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U51" t="n">
-        <v>0.989194044475331</v>
+        <v>0.1601137884062964</v>
       </c>
     </row>
     <row r="52">
@@ -3997,61 +3997,61 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>912962</v>
+        <v>964397</v>
       </c>
       <c r="D52" t="n">
+        <v>65</v>
+      </c>
+      <c r="E52" t="n">
+        <v>78</v>
+      </c>
+      <c r="F52" t="n">
+        <v>80</v>
+      </c>
+      <c r="G52" t="n">
+        <v>93</v>
+      </c>
+      <c r="H52" t="n">
         <v>59</v>
       </c>
-      <c r="E52" t="n">
-        <v>26</v>
-      </c>
-      <c r="F52" t="n">
-        <v>16</v>
-      </c>
-      <c r="G52" t="n">
-        <v>21</v>
-      </c>
-      <c r="H52" t="n">
-        <v>50</v>
-      </c>
       <c r="I52" t="n">
-        <v>89</v>
+        <v>7</v>
       </c>
       <c r="J52" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L52" t="n">
         <v>1</v>
       </c>
       <c r="M52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
         <v>1</v>
       </c>
       <c r="P52" t="n">
-        <v>2.269230769230769</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="Q52" t="n">
-        <v>0.7619047619047619</v>
+        <v>0.8602150537634409</v>
       </c>
       <c r="R52" t="n">
-        <v>0.5617977528089888</v>
+        <v>8.428571428571429</v>
       </c>
       <c r="S52" t="n">
-        <v>5.960453177072699</v>
+        <v>5.984256301052301</v>
       </c>
       <c r="T52" t="n">
         <v>1</v>
       </c>
       <c r="U52" t="n">
-        <v>0.8778522054770025</v>
+        <v>0.9905845960240393</v>
       </c>
     </row>
     <row r="53">
@@ -4066,61 +4066,61 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>42631</v>
+        <v>659515</v>
       </c>
       <c r="D53" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E53" t="n">
-        <v>93</v>
+        <v>37</v>
       </c>
       <c r="F53" t="n">
-        <v>59</v>
+        <v>97</v>
       </c>
       <c r="G53" t="n">
-        <v>10</v>
+        <v>84</v>
       </c>
       <c r="H53" t="n">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="I53" t="n">
-        <v>45</v>
+        <v>90</v>
       </c>
       <c r="J53" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="K53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M53" t="n">
         <v>1</v>
       </c>
       <c r="N53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
         <v>1</v>
       </c>
       <c r="P53" t="n">
-        <v>0.1075268817204301</v>
+        <v>0.4594594594594595</v>
       </c>
       <c r="Q53" t="n">
-        <v>5.9</v>
+        <v>1.154761904761905</v>
       </c>
       <c r="R53" t="n">
-        <v>0.6444444444444445</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="S53" t="n">
-        <v>4.629735707232856</v>
+        <v>5.819225336087723</v>
       </c>
       <c r="T53" t="n">
         <v>1</v>
       </c>
       <c r="U53" t="n">
-        <v>0.7931117218572744</v>
+        <v>0.599978556803992</v>
       </c>
     </row>
     <row r="54">
@@ -4135,31 +4135,31 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>107472</v>
+        <v>204518</v>
       </c>
       <c r="D54" t="n">
+        <v>44</v>
+      </c>
+      <c r="E54" t="n">
+        <v>35</v>
+      </c>
+      <c r="F54" t="n">
         <v>60</v>
       </c>
-      <c r="E54" t="n">
-        <v>31</v>
-      </c>
-      <c r="F54" t="n">
-        <v>26</v>
-      </c>
       <c r="G54" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H54" t="n">
-        <v>29</v>
+        <v>65</v>
       </c>
       <c r="I54" t="n">
-        <v>68</v>
+        <v>34</v>
       </c>
       <c r="J54" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K54" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
@@ -4168,28 +4168,28 @@
         <v>1</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P54" t="n">
-        <v>1.935483870967742</v>
+        <v>1.257142857142857</v>
       </c>
       <c r="Q54" t="n">
-        <v>0.4333333333333333</v>
+        <v>1.071428571428571</v>
       </c>
       <c r="R54" t="n">
-        <v>0.4264705882352941</v>
+        <v>1.911764705882353</v>
       </c>
       <c r="S54" t="n">
-        <v>5.031299371937026</v>
+        <v>5.310733660567585</v>
       </c>
       <c r="T54" t="n">
         <v>1</v>
       </c>
       <c r="U54" t="n">
-        <v>0.9361770854708559</v>
+        <v>0.9901558952743001</v>
       </c>
     </row>
     <row r="55">
@@ -4204,34 +4204,34 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>311236</v>
+        <v>392680</v>
       </c>
       <c r="D55" t="n">
-        <v>54</v>
+        <v>1</v>
       </c>
       <c r="E55" t="n">
-        <v>29</v>
+        <v>99</v>
       </c>
       <c r="F55" t="n">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="G55" t="n">
-        <v>72</v>
+        <v>50</v>
       </c>
       <c r="H55" t="n">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="I55" t="n">
-        <v>30</v>
+        <v>77</v>
       </c>
       <c r="J55" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="K55" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
         <v>0</v>
@@ -4243,22 +4243,22 @@
         <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>1.862068965517241</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="Q55" t="n">
-        <v>1.111111111111111</v>
+        <v>1.92</v>
       </c>
       <c r="R55" t="n">
-        <v>0.4666666666666667</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="S55" t="n">
-        <v>5.493091220517695</v>
+        <v>5.594039888296695</v>
       </c>
       <c r="T55" t="n">
         <v>1</v>
       </c>
       <c r="U55" t="n">
-        <v>0.5134605740355176</v>
+        <v>0.7936573687017782</v>
       </c>
     </row>
     <row r="56">
@@ -4273,61 +4273,61 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>748189</v>
+        <v>298841</v>
       </c>
       <c r="D56" t="n">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="E56" t="n">
-        <v>20</v>
+        <v>94</v>
       </c>
       <c r="F56" t="n">
+        <v>87</v>
+      </c>
+      <c r="G56" t="n">
+        <v>57</v>
+      </c>
+      <c r="H56" t="n">
+        <v>8</v>
+      </c>
+      <c r="I56" t="n">
         <v>53</v>
       </c>
-      <c r="G56" t="n">
-        <v>23</v>
-      </c>
-      <c r="H56" t="n">
-        <v>45</v>
-      </c>
-      <c r="I56" t="n">
-        <v>49</v>
-      </c>
       <c r="J56" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K56" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O56" t="n">
         <v>1</v>
       </c>
       <c r="P56" t="n">
-        <v>2.7</v>
+        <v>0.1808510638297872</v>
       </c>
       <c r="Q56" t="n">
-        <v>2.304347826086957</v>
+        <v>1.526315789473684</v>
       </c>
       <c r="R56" t="n">
-        <v>0.9183673469387755</v>
+        <v>0.1509433962264151</v>
       </c>
       <c r="S56" t="n">
-        <v>5.874011899299447</v>
+        <v>5.475441634262526</v>
       </c>
       <c r="T56" t="n">
         <v>1</v>
       </c>
       <c r="U56" t="n">
-        <v>0.8664798607699778</v>
+        <v>0.8913126298601852</v>
       </c>
     </row>
     <row r="57">
@@ -4342,61 +4342,61 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>379940</v>
+        <v>105190</v>
       </c>
       <c r="D57" t="n">
-        <v>22</v>
+        <v>62</v>
       </c>
       <c r="E57" t="n">
-        <v>1</v>
+        <v>76</v>
       </c>
       <c r="F57" t="n">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="G57" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="H57" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="I57" t="n">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="J57" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
       </c>
       <c r="P57" t="n">
-        <v>22</v>
+        <v>0.8157894736842105</v>
       </c>
       <c r="Q57" t="n">
-        <v>1.316666666666667</v>
+        <v>1.055555555555556</v>
       </c>
       <c r="R57" t="n">
-        <v>0.5609756097560976</v>
+        <v>0.410958904109589</v>
       </c>
       <c r="S57" t="n">
-        <v>5.57971616144886</v>
+        <v>5.021978583757437</v>
       </c>
       <c r="T57" t="n">
         <v>1</v>
       </c>
       <c r="U57" t="n">
-        <v>0.774458799348443</v>
+        <v>0.8542774768835674</v>
       </c>
     </row>
     <row r="58">
@@ -4411,61 +4411,61 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>912362</v>
+        <v>221579</v>
       </c>
       <c r="D58" t="n">
-        <v>78</v>
+        <v>35</v>
       </c>
       <c r="E58" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="F58" t="n">
-        <v>99</v>
+        <v>70</v>
       </c>
       <c r="G58" t="n">
-        <v>54</v>
+        <v>93</v>
       </c>
       <c r="H58" t="n">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="I58" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="J58" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="K58" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L58" t="n">
         <v>1</v>
       </c>
       <c r="M58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O58" t="n">
         <v>1</v>
       </c>
       <c r="P58" t="n">
-        <v>1.625</v>
+        <v>0.875</v>
       </c>
       <c r="Q58" t="n">
-        <v>1.833333333333333</v>
+        <v>0.7526881720430108</v>
       </c>
       <c r="R58" t="n">
-        <v>2.434782608695652</v>
+        <v>7.6</v>
       </c>
       <c r="S58" t="n">
-        <v>5.960167664568601</v>
+        <v>5.345530558034622</v>
       </c>
       <c r="T58" t="n">
         <v>1</v>
       </c>
       <c r="U58" t="n">
-        <v>0.9860864331350356</v>
+        <v>0.9870441763088867</v>
       </c>
     </row>
     <row r="59">
@@ -4480,61 +4480,61 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>749969</v>
+        <v>647368</v>
       </c>
       <c r="D59" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="E59" t="n">
-        <v>84</v>
+        <v>49</v>
       </c>
       <c r="F59" t="n">
-        <v>75</v>
+        <v>22</v>
       </c>
       <c r="G59" t="n">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="H59" t="n">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="I59" t="n">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="J59" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K59" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L59" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
         <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>0.7755102040816326</v>
       </c>
       <c r="Q59" t="n">
-        <v>1.442307692307692</v>
+        <v>0.360655737704918</v>
       </c>
       <c r="R59" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.2597402597402597</v>
       </c>
       <c r="S59" t="n">
-        <v>5.875043891264979</v>
+        <v>5.811151898879834</v>
       </c>
       <c r="T59" t="n">
         <v>1</v>
       </c>
       <c r="U59" t="n">
-        <v>0.757855245309676</v>
+        <v>0.6806643401647858</v>
       </c>
     </row>
     <row r="60">
@@ -4549,61 +4549,61 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>490489</v>
+        <v>836697</v>
       </c>
       <c r="D60" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E60" t="n">
-        <v>96</v>
+        <v>77</v>
       </c>
       <c r="F60" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="G60" t="n">
-        <v>13</v>
+        <v>47</v>
       </c>
       <c r="H60" t="n">
-        <v>56</v>
+        <v>18</v>
       </c>
       <c r="I60" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="J60" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
         <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O60" t="n">
         <v>1</v>
       </c>
       <c r="P60" t="n">
-        <v>0.40625</v>
+        <v>0.4805194805194805</v>
       </c>
       <c r="Q60" t="n">
-        <v>0.2307692307692308</v>
+        <v>0.2553191489361702</v>
       </c>
       <c r="R60" t="n">
-        <v>1.513513513513514</v>
+        <v>0.4186046511627907</v>
       </c>
       <c r="S60" t="n">
-        <v>5.690630157507832</v>
+        <v>5.92256873087169</v>
       </c>
       <c r="T60" t="n">
         <v>1</v>
       </c>
       <c r="U60" t="n">
-        <v>0.8998515149909784</v>
+        <v>0.982171112144934</v>
       </c>
     </row>
     <row r="61">
@@ -4618,25 +4618,25 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>769105</v>
+        <v>938008</v>
       </c>
       <c r="D61" t="n">
-        <v>2</v>
+        <v>53</v>
       </c>
       <c r="E61" t="n">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="F61" t="n">
-        <v>80</v>
+        <v>38</v>
       </c>
       <c r="G61" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="H61" t="n">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="I61" t="n">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="J61" t="n">
         <v>5</v>
@@ -4648,7 +4648,7 @@
         <v>2</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N61" t="n">
         <v>0</v>
@@ -4657,22 +4657,22 @@
         <v>0</v>
       </c>
       <c r="P61" t="n">
-        <v>0.02985074626865672</v>
+        <v>0.5824175824175825</v>
       </c>
       <c r="Q61" t="n">
-        <v>1.126760563380282</v>
+        <v>0.5066666666666667</v>
       </c>
       <c r="R61" t="n">
-        <v>1.189189189189189</v>
+        <v>0.2962962962962963</v>
       </c>
       <c r="S61" t="n">
-        <v>5.885986199414688</v>
+        <v>5.972207005363697</v>
       </c>
       <c r="T61" t="n">
         <v>1</v>
       </c>
       <c r="U61" t="n">
-        <v>0.7652168575493657</v>
+        <v>0.9898082338869757</v>
       </c>
     </row>
     <row r="62">
@@ -4687,28 +4687,28 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>671392</v>
+        <v>184116</v>
       </c>
       <c r="D62" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E62" t="n">
-        <v>25</v>
+        <v>71</v>
       </c>
       <c r="F62" t="n">
-        <v>92</v>
+        <v>21</v>
       </c>
       <c r="G62" t="n">
-        <v>90</v>
+        <v>36</v>
       </c>
       <c r="H62" t="n">
-        <v>57</v>
+        <v>85</v>
       </c>
       <c r="I62" t="n">
-        <v>90</v>
+        <v>3</v>
       </c>
       <c r="J62" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K62" t="n">
         <v>2</v>
@@ -4720,28 +4720,28 @@
         <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
       </c>
       <c r="P62" t="n">
-        <v>0.36</v>
+        <v>0.02816901408450704</v>
       </c>
       <c r="Q62" t="n">
-        <v>1.022222222222222</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="R62" t="n">
-        <v>0.6333333333333333</v>
+        <v>28.33333333333333</v>
       </c>
       <c r="S62" t="n">
-        <v>5.826976808944729</v>
+        <v>5.265093889890956</v>
       </c>
       <c r="T62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U62" t="n">
-        <v>0.8826095095904318</v>
+        <v>0.3296142508471608</v>
       </c>
     </row>
     <row r="63">
@@ -4756,61 +4756,61 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>914572</v>
+        <v>76678</v>
       </c>
       <c r="D63" t="n">
-        <v>38</v>
+        <v>88</v>
       </c>
       <c r="E63" t="n">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="F63" t="n">
-        <v>13</v>
+        <v>77</v>
       </c>
       <c r="G63" t="n">
+        <v>69</v>
+      </c>
+      <c r="H63" t="n">
+        <v>33</v>
+      </c>
+      <c r="I63" t="n">
         <v>46</v>
       </c>
-      <c r="H63" t="n">
-        <v>59</v>
-      </c>
-      <c r="I63" t="n">
-        <v>23</v>
-      </c>
       <c r="J63" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N63" t="n">
         <v>1</v>
       </c>
       <c r="O63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P63" t="n">
-        <v>0.4418604651162791</v>
+        <v>1.128205128205128</v>
       </c>
       <c r="Q63" t="n">
-        <v>0.2826086956521739</v>
+        <v>1.115942028985507</v>
       </c>
       <c r="R63" t="n">
-        <v>2.565217391304348</v>
+        <v>0.7173913043478261</v>
       </c>
       <c r="S63" t="n">
-        <v>5.961218376003665</v>
+        <v>4.884676440443456</v>
       </c>
       <c r="T63" t="n">
         <v>1</v>
       </c>
       <c r="U63" t="n">
-        <v>0.9517402924122612</v>
+        <v>0.9914330366819226</v>
       </c>
     </row>
     <row r="64">
@@ -4825,61 +4825,61 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>349688</v>
+        <v>29017</v>
       </c>
       <c r="D64" t="n">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="E64" t="n">
+        <v>49</v>
+      </c>
+      <c r="F64" t="n">
         <v>37</v>
       </c>
-      <c r="F64" t="n">
-        <v>9</v>
-      </c>
       <c r="G64" t="n">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="H64" t="n">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="I64" t="n">
-        <v>58</v>
+        <v>10</v>
       </c>
       <c r="J64" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="K64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M64" t="n">
         <v>1</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
       </c>
       <c r="P64" t="n">
-        <v>1.648648648648649</v>
+        <v>1.897959183673469</v>
       </c>
       <c r="Q64" t="n">
-        <v>1.5</v>
+        <v>1.027777777777778</v>
       </c>
       <c r="R64" t="n">
-        <v>0.8275862068965517</v>
+        <v>7.3</v>
       </c>
       <c r="S64" t="n">
-        <v>5.54368197112984</v>
+        <v>4.462667476368572</v>
       </c>
       <c r="T64" t="n">
         <v>1</v>
       </c>
       <c r="U64" t="n">
-        <v>0.9090573335247352</v>
+        <v>0.9070244352850615</v>
       </c>
     </row>
     <row r="65">
@@ -4894,61 +4894,61 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>866243</v>
+        <v>270321</v>
       </c>
       <c r="D65" t="n">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="E65" t="n">
-        <v>83</v>
+        <v>22</v>
       </c>
       <c r="F65" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="G65" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="H65" t="n">
-        <v>35</v>
+        <v>79</v>
       </c>
       <c r="I65" t="n">
-        <v>57</v>
+        <v>12</v>
       </c>
       <c r="J65" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="K65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
         <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
       </c>
       <c r="P65" t="n">
-        <v>1.024096385542169</v>
+        <v>4.227272727272728</v>
       </c>
       <c r="Q65" t="n">
-        <v>2.884615384615385</v>
+        <v>36</v>
       </c>
       <c r="R65" t="n">
-        <v>0.6140350877192983</v>
+        <v>6.583333333333333</v>
       </c>
       <c r="S65" t="n">
-        <v>5.937640239509138</v>
+        <v>5.431881391942893</v>
       </c>
       <c r="T65" t="n">
         <v>1</v>
       </c>
       <c r="U65" t="n">
-        <v>0.9670923234566524</v>
+        <v>0.8898649566765566</v>
       </c>
     </row>
     <row r="66">
@@ -4963,34 +4963,34 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>212414</v>
+        <v>493565</v>
       </c>
       <c r="D66" t="n">
-        <v>86</v>
+        <v>17</v>
       </c>
       <c r="E66" t="n">
-        <v>43</v>
+        <v>88</v>
       </c>
       <c r="F66" t="n">
+        <v>3</v>
+      </c>
+      <c r="G66" t="n">
+        <v>49</v>
+      </c>
+      <c r="H66" t="n">
         <v>4</v>
       </c>
-      <c r="G66" t="n">
-        <v>79</v>
-      </c>
-      <c r="H66" t="n">
-        <v>42</v>
-      </c>
       <c r="I66" t="n">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="J66" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L66" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M66" t="n">
         <v>1</v>
@@ -4999,25 +4999,25 @@
         <v>0</v>
       </c>
       <c r="O66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P66" t="n">
-        <v>2</v>
+        <v>0.1931818181818182</v>
       </c>
       <c r="Q66" t="n">
-        <v>0.05063291139240506</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="R66" t="n">
-        <v>0.5915492957746479</v>
+        <v>0.05970149253731343</v>
       </c>
       <c r="S66" t="n">
-        <v>5.327185181840743</v>
+        <v>5.693345235058893</v>
       </c>
       <c r="T66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U66" t="n">
-        <v>0.3868968731030716</v>
+        <v>0.966068102563152</v>
       </c>
     </row>
     <row r="67">
@@ -5032,34 +5032,34 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>912173</v>
+        <v>965105</v>
       </c>
       <c r="D67" t="n">
-        <v>91</v>
+        <v>43</v>
       </c>
       <c r="E67" t="n">
-        <v>33</v>
+        <v>57</v>
       </c>
       <c r="F67" t="n">
-        <v>11</v>
+        <v>95</v>
       </c>
       <c r="G67" t="n">
-        <v>76</v>
+        <v>21</v>
       </c>
       <c r="H67" t="n">
-        <v>9</v>
+        <v>67</v>
       </c>
       <c r="I67" t="n">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="J67" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L67" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
         <v>1</v>
@@ -5071,22 +5071,22 @@
         <v>0</v>
       </c>
       <c r="P67" t="n">
-        <v>2.757575757575758</v>
+        <v>0.7543859649122807</v>
       </c>
       <c r="Q67" t="n">
-        <v>0.1447368421052632</v>
+        <v>4.523809523809524</v>
       </c>
       <c r="R67" t="n">
-        <v>0.1451612903225807</v>
+        <v>1.395833333333333</v>
       </c>
       <c r="S67" t="n">
-        <v>5.960077689240753</v>
+        <v>5.984575015610019</v>
       </c>
       <c r="T67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U67" t="n">
-        <v>0.3215228044603875</v>
+        <v>0.9853878443833373</v>
       </c>
     </row>
     <row r="68">
@@ -5101,34 +5101,34 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>25675</v>
+        <v>358322</v>
       </c>
       <c r="D68" t="n">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="E68" t="n">
-        <v>69</v>
+        <v>44</v>
       </c>
       <c r="F68" t="n">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="G68" t="n">
-        <v>45</v>
+        <v>79</v>
       </c>
       <c r="H68" t="n">
+        <v>22</v>
+      </c>
+      <c r="I68" t="n">
+        <v>81</v>
+      </c>
+      <c r="J68" t="n">
         <v>3</v>
       </c>
-      <c r="I68" t="n">
-        <v>56</v>
-      </c>
-      <c r="J68" t="n">
-        <v>2</v>
-      </c>
       <c r="K68" t="n">
         <v>1</v>
       </c>
       <c r="L68" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M68" t="n">
         <v>0</v>
@@ -5137,25 +5137,25 @@
         <v>1</v>
       </c>
       <c r="O68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P68" t="n">
-        <v>0.1159420289855072</v>
+        <v>0.7954545454545454</v>
       </c>
       <c r="Q68" t="n">
-        <v>1.222222222222222</v>
+        <v>0.8607594936708861</v>
       </c>
       <c r="R68" t="n">
-        <v>0.05357142857142857</v>
+        <v>0.2716049382716049</v>
       </c>
       <c r="S68" t="n">
-        <v>4.40952736701224</v>
+        <v>5.554274685510508</v>
       </c>
       <c r="T68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U68" t="n">
-        <v>0.4600546433582165</v>
+        <v>0.9817528848214438</v>
       </c>
     </row>
     <row r="69">
@@ -5170,31 +5170,31 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>831897</v>
+        <v>68363</v>
       </c>
       <c r="D69" t="n">
-        <v>39</v>
+        <v>94</v>
       </c>
       <c r="E69" t="n">
-        <v>77</v>
+        <v>40</v>
       </c>
       <c r="F69" t="n">
-        <v>34</v>
+        <v>83</v>
       </c>
       <c r="G69" t="n">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="H69" t="n">
-        <v>82</v>
+        <v>57</v>
       </c>
       <c r="I69" t="n">
-        <v>36</v>
+        <v>74</v>
       </c>
       <c r="J69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L69" t="n">
         <v>2</v>
@@ -5206,25 +5206,25 @@
         <v>1</v>
       </c>
       <c r="O69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P69" t="n">
-        <v>0.5064935064935064</v>
+        <v>2.35</v>
       </c>
       <c r="Q69" t="n">
-        <v>0.4788732394366197</v>
+        <v>1.360655737704918</v>
       </c>
       <c r="R69" t="n">
-        <v>2.277777777777778</v>
+        <v>0.7702702702702703</v>
       </c>
       <c r="S69" t="n">
-        <v>5.920070080193656</v>
+        <v>4.834827465504305</v>
       </c>
       <c r="T69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U69" t="n">
-        <v>0.6204850673297585</v>
+        <v>0.35518897865458</v>
       </c>
     </row>
     <row r="70">
@@ -5239,34 +5239,34 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>206988</v>
+        <v>272162</v>
       </c>
       <c r="D70" t="n">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="E70" t="n">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="F70" t="n">
-        <v>81</v>
+        <v>42</v>
       </c>
       <c r="G70" t="n">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="H70" t="n">
-        <v>2</v>
+        <v>91</v>
       </c>
       <c r="I70" t="n">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="J70" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K70" t="n">
         <v>1</v>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M70" t="n">
         <v>0</v>
@@ -5278,22 +5278,22 @@
         <v>0</v>
       </c>
       <c r="P70" t="n">
-        <v>1.052631578947368</v>
+        <v>0.8367346938775511</v>
       </c>
       <c r="Q70" t="n">
-        <v>1.421052631578947</v>
+        <v>0.8076923076923077</v>
       </c>
       <c r="R70" t="n">
-        <v>0.1428571428571428</v>
+        <v>2.219512195121951</v>
       </c>
       <c r="S70" t="n">
-        <v>5.315947266392971</v>
+        <v>5.434829083438779</v>
       </c>
       <c r="T70" t="n">
         <v>1</v>
       </c>
       <c r="U70" t="n">
-        <v>0.9374338996403396</v>
+        <v>0.990815765022002</v>
       </c>
     </row>
     <row r="71">
@@ -5308,61 +5308,61 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>827556</v>
+        <v>841343</v>
       </c>
       <c r="D71" t="n">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="E71" t="n">
-        <v>71</v>
+        <v>27</v>
       </c>
       <c r="F71" t="n">
-        <v>58</v>
+        <v>5</v>
       </c>
       <c r="G71" t="n">
-        <v>74</v>
+        <v>22</v>
       </c>
       <c r="H71" t="n">
-        <v>35</v>
+        <v>95</v>
       </c>
       <c r="I71" t="n">
-        <v>89</v>
+        <v>28</v>
       </c>
       <c r="J71" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K71" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M71" t="n">
         <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P71" t="n">
-        <v>1.211267605633803</v>
+        <v>2.962962962962963</v>
       </c>
       <c r="Q71" t="n">
-        <v>0.7837837837837838</v>
+        <v>0.2272727272727273</v>
       </c>
       <c r="R71" t="n">
-        <v>0.3932584269662922</v>
+        <v>3.392857142857143</v>
       </c>
       <c r="S71" t="n">
-        <v>5.917797916566096</v>
+        <v>5.924973601928236</v>
       </c>
       <c r="T71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U71" t="n">
-        <v>0.9943208849735079</v>
+        <v>0.3641291468049459</v>
       </c>
     </row>
     <row r="72">
@@ -5377,61 +5377,61 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>482353</v>
+        <v>221326</v>
       </c>
       <c r="D72" t="n">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="E72" t="n">
-        <v>98</v>
+        <v>7</v>
       </c>
       <c r="F72" t="n">
-        <v>99</v>
+        <v>54</v>
       </c>
       <c r="G72" t="n">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="H72" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="I72" t="n">
-        <v>25</v>
+        <v>97</v>
       </c>
       <c r="J72" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P72" t="n">
-        <v>0.2142857142857143</v>
+        <v>13</v>
       </c>
       <c r="Q72" t="n">
-        <v>1.903846153846154</v>
+        <v>0.84375</v>
       </c>
       <c r="R72" t="n">
-        <v>0.4</v>
+        <v>0.154639175257732</v>
       </c>
       <c r="S72" t="n">
-        <v>5.683365884333747</v>
+        <v>5.345034397369416</v>
       </c>
       <c r="T72" t="n">
         <v>1</v>
       </c>
       <c r="U72" t="n">
-        <v>0.8395913200953619</v>
+        <v>0.8316499133492889</v>
       </c>
     </row>
     <row r="73">
@@ -5446,61 +5446,61 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>666089</v>
+        <v>863083</v>
       </c>
       <c r="D73" t="n">
-        <v>63</v>
+        <v>21</v>
       </c>
       <c r="E73" t="n">
-        <v>52</v>
+        <v>12</v>
       </c>
       <c r="F73" t="n">
+        <v>29</v>
+      </c>
+      <c r="G73" t="n">
         <v>22</v>
       </c>
-      <c r="G73" t="n">
-        <v>95</v>
-      </c>
       <c r="H73" t="n">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="I73" t="n">
         <v>6</v>
       </c>
       <c r="J73" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="K73" t="n">
         <v>1</v>
       </c>
       <c r="L73" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P73" t="n">
-        <v>1.211538461538461</v>
+        <v>1.75</v>
       </c>
       <c r="Q73" t="n">
-        <v>0.2315789473684211</v>
+        <v>1.318181818181818</v>
       </c>
       <c r="R73" t="n">
-        <v>9.333333333333334</v>
+        <v>5.333333333333333</v>
       </c>
       <c r="S73" t="n">
-        <v>5.823532913648723</v>
+        <v>5.936053065658629</v>
       </c>
       <c r="T73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U73" t="n">
-        <v>0.9860435163040395</v>
+        <v>0.3804547348987202</v>
       </c>
     </row>
     <row r="74">
@@ -5515,31 +5515,31 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>792932</v>
+        <v>999246</v>
       </c>
       <c r="D74" t="n">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="E74" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="F74" t="n">
-        <v>43</v>
+        <v>76</v>
       </c>
       <c r="G74" t="n">
-        <v>80</v>
+        <v>18</v>
       </c>
       <c r="H74" t="n">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="I74" t="n">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="J74" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K74" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L74" t="n">
         <v>2</v>
@@ -5551,25 +5551,25 @@
         <v>1</v>
       </c>
       <c r="O74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P74" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.8727272727272727</v>
       </c>
       <c r="Q74" t="n">
-        <v>0.5375</v>
+        <v>4.222222222222222</v>
       </c>
       <c r="R74" t="n">
-        <v>1.414285714285714</v>
+        <v>10.625</v>
       </c>
       <c r="S74" t="n">
-        <v>5.899236492538814</v>
+        <v>5.999672853068843</v>
       </c>
       <c r="T74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U74" t="n">
-        <v>0.329480238635082</v>
+        <v>0.9863632615801596</v>
       </c>
     </row>
     <row r="75">
@@ -5584,28 +5584,28 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>572822</v>
+        <v>292557</v>
       </c>
       <c r="D75" t="n">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="E75" t="n">
-        <v>74</v>
+        <v>27</v>
       </c>
       <c r="F75" t="n">
-        <v>63</v>
+        <v>14</v>
       </c>
       <c r="G75" t="n">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="H75" t="n">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="I75" t="n">
-        <v>90</v>
+        <v>53</v>
       </c>
       <c r="J75" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K75" t="n">
         <v>2</v>
@@ -5620,25 +5620,25 @@
         <v>1</v>
       </c>
       <c r="O75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P75" t="n">
-        <v>1.324324324324324</v>
+        <v>2.740740740740741</v>
       </c>
       <c r="Q75" t="n">
-        <v>4.5</v>
+        <v>0.4516129032258064</v>
       </c>
       <c r="R75" t="n">
-        <v>1.022222222222222</v>
+        <v>1.566037735849057</v>
       </c>
       <c r="S75" t="n">
-        <v>5.758020447450194</v>
+        <v>5.466211978393932</v>
       </c>
       <c r="T75" t="n">
         <v>1</v>
       </c>
       <c r="U75" t="n">
-        <v>0.6433303563580612</v>
+        <v>0.8912478459607932</v>
       </c>
     </row>
     <row r="76">
@@ -5653,28 +5653,28 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>776145</v>
+        <v>449370</v>
       </c>
       <c r="D76" t="n">
-        <v>93</v>
+        <v>68</v>
       </c>
       <c r="E76" t="n">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="F76" t="n">
-        <v>85</v>
+        <v>4</v>
       </c>
       <c r="G76" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="H76" t="n">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="I76" t="n">
-        <v>95</v>
+        <v>45</v>
       </c>
       <c r="J76" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="K76" t="n">
         <v>2</v>
@@ -5683,31 +5683,31 @@
         <v>2</v>
       </c>
       <c r="M76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N76" t="n">
         <v>0</v>
       </c>
       <c r="O76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P76" t="n">
-        <v>2.384615384615385</v>
+        <v>7.555555555555555</v>
       </c>
       <c r="Q76" t="n">
-        <v>2.5</v>
+        <v>0.0975609756097561</v>
       </c>
       <c r="R76" t="n">
-        <v>0.2631578947368421</v>
+        <v>1.133333333333333</v>
       </c>
       <c r="S76" t="n">
-        <v>5.889943423616788</v>
+        <v>5.65260504194524</v>
       </c>
       <c r="T76" t="n">
         <v>1</v>
       </c>
       <c r="U76" t="n">
-        <v>0.918000137189297</v>
+        <v>0.8169804696938335</v>
       </c>
     </row>
     <row r="77">
@@ -5722,61 +5722,61 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>871641</v>
+        <v>157244</v>
       </c>
       <c r="D77" t="n">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="E77" t="n">
+        <v>21</v>
+      </c>
+      <c r="F77" t="n">
+        <v>52</v>
+      </c>
+      <c r="G77" t="n">
+        <v>88</v>
+      </c>
+      <c r="H77" t="n">
         <v>15</v>
       </c>
-      <c r="F77" t="n">
-        <v>77</v>
-      </c>
-      <c r="G77" t="n">
-        <v>51</v>
-      </c>
-      <c r="H77" t="n">
-        <v>52</v>
-      </c>
       <c r="I77" t="n">
-        <v>14</v>
+        <v>54</v>
       </c>
       <c r="J77" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P77" t="n">
-        <v>1.8</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="Q77" t="n">
-        <v>1.509803921568627</v>
+        <v>0.5909090909090909</v>
       </c>
       <c r="R77" t="n">
-        <v>3.714285714285714</v>
+        <v>0.2777777777777778</v>
       </c>
       <c r="S77" t="n">
-        <v>5.940338148523251</v>
+        <v>5.196576844852233</v>
       </c>
       <c r="T77" t="n">
         <v>1</v>
       </c>
       <c r="U77" t="n">
-        <v>0.9215954448967965</v>
+        <v>0.7877521428232491</v>
       </c>
     </row>
     <row r="78">
@@ -5791,61 +5791,61 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>346889</v>
+        <v>251211</v>
       </c>
       <c r="D78" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="E78" t="n">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="F78" t="n">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="G78" t="n">
-        <v>77</v>
+        <v>19</v>
       </c>
       <c r="H78" t="n">
-        <v>66</v>
+        <v>29</v>
       </c>
       <c r="I78" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="J78" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="K78" t="n">
         <v>2</v>
       </c>
       <c r="L78" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N78" t="n">
         <v>1</v>
       </c>
       <c r="O78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P78" t="n">
-        <v>0.7619047619047619</v>
+        <v>0.7254901960784313</v>
       </c>
       <c r="Q78" t="n">
-        <v>0.4415584415584415</v>
+        <v>1.210526315789474</v>
       </c>
       <c r="R78" t="n">
-        <v>22</v>
+        <v>1.208333333333333</v>
       </c>
       <c r="S78" t="n">
-        <v>5.540191780362623</v>
+        <v>5.400040381121319</v>
       </c>
       <c r="T78" t="n">
         <v>1</v>
       </c>
       <c r="U78" t="n">
-        <v>0.7209375804557577</v>
+        <v>0.9707924081614843</v>
       </c>
     </row>
     <row r="79">
@@ -5860,61 +5860,61 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>127791</v>
+        <v>400731</v>
       </c>
       <c r="D79" t="n">
-        <v>19</v>
+        <v>98</v>
       </c>
       <c r="E79" t="n">
-        <v>37</v>
+        <v>71</v>
       </c>
       <c r="F79" t="n">
-        <v>76</v>
+        <v>27</v>
       </c>
       <c r="G79" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="H79" t="n">
-        <v>99</v>
+        <v>13</v>
       </c>
       <c r="I79" t="n">
-        <v>84</v>
+        <v>27</v>
       </c>
       <c r="J79" t="n">
         <v>9</v>
       </c>
       <c r="K79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L79" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
       </c>
       <c r="P79" t="n">
-        <v>0.5135135135135135</v>
+        <v>1.380281690140845</v>
       </c>
       <c r="Q79" t="n">
-        <v>1.490196078431373</v>
+        <v>0.4821428571428572</v>
       </c>
       <c r="R79" t="n">
-        <v>1.178571428571429</v>
+        <v>0.4814814814814815</v>
       </c>
       <c r="S79" t="n">
-        <v>5.106503667088396</v>
+        <v>5.602854023911424</v>
       </c>
       <c r="T79" t="n">
         <v>1</v>
       </c>
       <c r="U79" t="n">
-        <v>0.9803987320550214</v>
+        <v>0.9774762609232962</v>
       </c>
     </row>
     <row r="80">
@@ -5929,37 +5929,37 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>939563</v>
+        <v>33035</v>
       </c>
       <c r="D80" t="n">
         <v>23</v>
       </c>
       <c r="E80" t="n">
-        <v>10</v>
+        <v>88</v>
       </c>
       <c r="F80" t="n">
-        <v>88</v>
+        <v>61</v>
       </c>
       <c r="G80" t="n">
-        <v>67</v>
+        <v>17</v>
       </c>
       <c r="H80" t="n">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="I80" t="n">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="J80" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="K80" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L80" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N80" t="n">
         <v>1</v>
@@ -5968,22 +5968,22 @@
         <v>1</v>
       </c>
       <c r="P80" t="n">
-        <v>2.3</v>
+        <v>0.2613636363636364</v>
       </c>
       <c r="Q80" t="n">
-        <v>1.313432835820896</v>
+        <v>3.588235294117647</v>
       </c>
       <c r="R80" t="n">
-        <v>3.4375</v>
+        <v>0.75</v>
       </c>
       <c r="S80" t="n">
-        <v>5.972926368151471</v>
+        <v>4.518987457440955</v>
       </c>
       <c r="T80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U80" t="n">
-        <v>0.8923287058467644</v>
+        <v>0.4995511912806193</v>
       </c>
     </row>
     <row r="81">
@@ -5998,61 +5998,61 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>506042</v>
+        <v>829086</v>
       </c>
       <c r="D81" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="E81" t="n">
-        <v>63</v>
+        <v>26</v>
       </c>
       <c r="F81" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G81" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="H81" t="n">
-        <v>58</v>
+        <v>97</v>
       </c>
       <c r="I81" t="n">
-        <v>14</v>
+        <v>62</v>
       </c>
       <c r="J81" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K81" t="n">
         <v>1</v>
       </c>
       <c r="L81" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P81" t="n">
-        <v>0.2698412698412698</v>
+        <v>0.9615384615384616</v>
       </c>
       <c r="Q81" t="n">
-        <v>1.316666666666667</v>
+        <v>3.9</v>
       </c>
       <c r="R81" t="n">
-        <v>4.142857142857143</v>
+        <v>1.564516129032258</v>
       </c>
       <c r="S81" t="n">
-        <v>5.704187421719795</v>
+        <v>5.918600105504978</v>
       </c>
       <c r="T81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U81" t="n">
-        <v>0.4698567870487894</v>
+        <v>0.9688407527075823</v>
       </c>
     </row>
     <row r="82">
@@ -6067,61 +6067,61 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>24457</v>
+        <v>171577</v>
       </c>
       <c r="D82" t="n">
-        <v>68</v>
+        <v>28</v>
       </c>
       <c r="E82" t="n">
-        <v>70</v>
+        <v>23</v>
       </c>
       <c r="F82" t="n">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="G82" t="n">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="H82" t="n">
+        <v>57</v>
+      </c>
+      <c r="I82" t="n">
+        <v>25</v>
+      </c>
+      <c r="J82" t="n">
         <v>9</v>
       </c>
-      <c r="I82" t="n">
-        <v>28</v>
-      </c>
-      <c r="J82" t="n">
-        <v>2</v>
-      </c>
       <c r="K82" t="n">
         <v>1</v>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N82" t="n">
         <v>0</v>
       </c>
       <c r="O82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P82" t="n">
-        <v>0.9714285714285714</v>
+        <v>1.217391304347826</v>
       </c>
       <c r="Q82" t="n">
-        <v>0.8478260869565217</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="R82" t="n">
-        <v>0.3214285714285715</v>
+        <v>2.28</v>
       </c>
       <c r="S82" t="n">
-        <v>4.388420940661169</v>
+        <v>5.234461601163498</v>
       </c>
       <c r="T82" t="n">
         <v>1</v>
       </c>
       <c r="U82" t="n">
-        <v>0.8795494461799451</v>
+        <v>0.9601176336970073</v>
       </c>
     </row>
     <row r="83">
@@ -6136,37 +6136,37 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>529211</v>
+        <v>691628</v>
       </c>
       <c r="D83" t="n">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="E83" t="n">
-        <v>83</v>
+        <v>28</v>
       </c>
       <c r="F83" t="n">
-        <v>3</v>
+        <v>81</v>
       </c>
       <c r="G83" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="H83" t="n">
+        <v>46</v>
+      </c>
+      <c r="I83" t="n">
+        <v>72</v>
+      </c>
+      <c r="J83" t="n">
         <v>7</v>
       </c>
-      <c r="I83" t="n">
-        <v>11</v>
-      </c>
-      <c r="J83" t="n">
-        <v>4</v>
-      </c>
       <c r="K83" t="n">
         <v>0</v>
       </c>
       <c r="L83" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N83" t="n">
         <v>0</v>
@@ -6175,22 +6175,22 @@
         <v>1</v>
       </c>
       <c r="P83" t="n">
-        <v>0.6144578313253012</v>
+        <v>2.035714285714286</v>
       </c>
       <c r="Q83" t="n">
-        <v>0.04545454545454546</v>
+        <v>1.306451612903226</v>
       </c>
       <c r="R83" t="n">
-        <v>0.6363636363636364</v>
+        <v>0.6388888888888888</v>
       </c>
       <c r="S83" t="n">
-        <v>5.723629683351246</v>
+        <v>5.839873194948801</v>
       </c>
       <c r="T83" t="n">
         <v>1</v>
       </c>
       <c r="U83" t="n">
-        <v>0.9730645479789078</v>
+        <v>0.8965507019686555</v>
       </c>
     </row>
     <row r="84">
@@ -6205,61 +6205,61 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>816840</v>
+        <v>651278</v>
       </c>
       <c r="D84" t="n">
-        <v>11</v>
+        <v>97</v>
       </c>
       <c r="E84" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="F84" t="n">
-        <v>89</v>
+        <v>53</v>
       </c>
       <c r="G84" t="n">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="H84" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="I84" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="J84" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M84" t="n">
         <v>0</v>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O84" t="n">
         <v>1</v>
       </c>
       <c r="P84" t="n">
-        <v>0</v>
+        <v>1.276315789473684</v>
       </c>
       <c r="Q84" t="n">
-        <v>2.696969696969697</v>
+        <v>1.152173913043478</v>
       </c>
       <c r="R84" t="n">
-        <v>0.6875</v>
+        <v>0</v>
       </c>
       <c r="S84" t="n">
-        <v>5.912137528328214</v>
+        <v>5.813767074901927</v>
       </c>
       <c r="T84" t="n">
         <v>1</v>
       </c>
       <c r="U84" t="n">
-        <v>0.7596131574427861</v>
+        <v>0.7172584364382928</v>
       </c>
     </row>
     <row r="85">
@@ -6274,61 +6274,61 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>298511</v>
+        <v>198603</v>
       </c>
       <c r="D85" t="n">
-        <v>99</v>
+        <v>66</v>
       </c>
       <c r="E85" t="n">
-        <v>13</v>
+        <v>65</v>
       </c>
       <c r="F85" t="n">
-        <v>24</v>
+        <v>98</v>
       </c>
       <c r="G85" t="n">
-        <v>7</v>
+        <v>65</v>
       </c>
       <c r="H85" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I85" t="n">
-        <v>97</v>
+        <v>4</v>
       </c>
       <c r="J85" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K85" t="n">
         <v>2</v>
       </c>
       <c r="L85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N85" t="n">
         <v>1</v>
       </c>
       <c r="O85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P85" t="n">
-        <v>7.615384615384615</v>
+        <v>1.015384615384615</v>
       </c>
       <c r="Q85" t="n">
-        <v>3.428571428571428</v>
+        <v>1.507692307692308</v>
       </c>
       <c r="R85" t="n">
-        <v>0.05154639175257732</v>
+        <v>2.5</v>
       </c>
       <c r="S85" t="n">
-        <v>5.47496179418911</v>
+        <v>5.29798799119075</v>
       </c>
       <c r="T85" t="n">
         <v>1</v>
       </c>
       <c r="U85" t="n">
-        <v>0.7853658361844762</v>
+        <v>0.9718149108599949</v>
       </c>
     </row>
     <row r="86">
@@ -6343,31 +6343,31 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>352291</v>
+        <v>876573</v>
       </c>
       <c r="D86" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E86" t="n">
-        <v>1</v>
+        <v>43</v>
       </c>
       <c r="F86" t="n">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="G86" t="n">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="H86" t="n">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="I86" t="n">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="J86" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="K86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L86" t="n">
         <v>0</v>
@@ -6382,22 +6382,22 @@
         <v>1</v>
       </c>
       <c r="P86" t="n">
-        <v>65</v>
+        <v>1.488372093023256</v>
       </c>
       <c r="Q86" t="n">
-        <v>1.423076923076923</v>
+        <v>2.75</v>
       </c>
       <c r="R86" t="n">
-        <v>1.67741935483871</v>
+        <v>2.5</v>
       </c>
       <c r="S86" t="n">
-        <v>5.546902781145183</v>
+        <v>5.942788584930776</v>
       </c>
       <c r="T86" t="n">
         <v>1</v>
       </c>
       <c r="U86" t="n">
-        <v>0.8063432185112969</v>
+        <v>0.9597819242735329</v>
       </c>
     </row>
     <row r="87">
@@ -6412,37 +6412,37 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>444121</v>
+        <v>178245</v>
       </c>
       <c r="D87" t="n">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="E87" t="n">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="F87" t="n">
-        <v>52</v>
+        <v>73</v>
       </c>
       <c r="G87" t="n">
-        <v>12</v>
+        <v>93</v>
       </c>
       <c r="H87" t="n">
+        <v>7</v>
+      </c>
+      <c r="I87" t="n">
         <v>6</v>
       </c>
-      <c r="I87" t="n">
-        <v>3</v>
-      </c>
       <c r="J87" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K87" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N87" t="n">
         <v>1</v>
@@ -6451,22 +6451,22 @@
         <v>0</v>
       </c>
       <c r="P87" t="n">
-        <v>2.380952380952381</v>
+        <v>0.8048780487804879</v>
       </c>
       <c r="Q87" t="n">
-        <v>4.333333333333333</v>
+        <v>0.7849462365591398</v>
       </c>
       <c r="R87" t="n">
-        <v>2</v>
+        <v>1.166666666666667</v>
       </c>
       <c r="S87" t="n">
-        <v>5.647502286891201</v>
+        <v>5.251019792675828</v>
       </c>
       <c r="T87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U87" t="n">
-        <v>0.4415131525616786</v>
+        <v>0.9733910514317549</v>
       </c>
     </row>
     <row r="88">
@@ -6481,61 +6481,61 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>256135</v>
+        <v>500865</v>
       </c>
       <c r="D88" t="n">
-        <v>80</v>
+        <v>10</v>
       </c>
       <c r="E88" t="n">
-        <v>31</v>
+        <v>99</v>
       </c>
       <c r="F88" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G88" t="n">
-        <v>84</v>
+        <v>25</v>
       </c>
       <c r="H88" t="n">
-        <v>12</v>
+        <v>71</v>
       </c>
       <c r="I88" t="n">
-        <v>51</v>
+        <v>11</v>
       </c>
       <c r="J88" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="K88" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M88" t="n">
         <v>0</v>
       </c>
       <c r="N88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
       </c>
       <c r="P88" t="n">
-        <v>2.580645161290323</v>
+        <v>0.101010101010101</v>
       </c>
       <c r="Q88" t="n">
-        <v>1.083333333333333</v>
+        <v>3.56</v>
       </c>
       <c r="R88" t="n">
-        <v>0.2352941176470588</v>
+        <v>6.454545454545454</v>
       </c>
       <c r="S88" t="n">
-        <v>5.408470622992338</v>
+        <v>5.699721551726348</v>
       </c>
       <c r="T88" t="n">
         <v>1</v>
       </c>
       <c r="U88" t="n">
-        <v>0.8760053529178415</v>
+        <v>0.7990863719797177</v>
       </c>
     </row>
     <row r="89">
@@ -6550,34 +6550,34 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>52936</v>
+        <v>487835</v>
       </c>
       <c r="D89" t="n">
-        <v>42</v>
+        <v>78</v>
       </c>
       <c r="E89" t="n">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="F89" t="n">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="G89" t="n">
-        <v>48</v>
+        <v>15</v>
       </c>
       <c r="H89" t="n">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="I89" t="n">
-        <v>13</v>
+        <v>77</v>
       </c>
       <c r="J89" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K89" t="n">
         <v>0</v>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M89" t="n">
         <v>1</v>
@@ -6589,22 +6589,22 @@
         <v>1</v>
       </c>
       <c r="P89" t="n">
-        <v>0.6363636363636364</v>
+        <v>0.975</v>
       </c>
       <c r="Q89" t="n">
-        <v>0.9375</v>
+        <v>1</v>
       </c>
       <c r="R89" t="n">
-        <v>3.769230769230769</v>
+        <v>1.038961038961039</v>
       </c>
       <c r="S89" t="n">
-        <v>4.723759325700446</v>
+        <v>5.688273846048344</v>
       </c>
       <c r="T89" t="n">
         <v>1</v>
       </c>
       <c r="U89" t="n">
-        <v>0.9740026299319828</v>
+        <v>0.8147627944367057</v>
       </c>
     </row>
     <row r="90">
@@ -6619,31 +6619,31 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>100697</v>
+        <v>874065</v>
       </c>
       <c r="D90" t="n">
-        <v>28</v>
+        <v>71</v>
       </c>
       <c r="E90" t="n">
+        <v>92</v>
+      </c>
+      <c r="F90" t="n">
         <v>97</v>
       </c>
-      <c r="F90" t="n">
-        <v>73</v>
-      </c>
       <c r="G90" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="H90" t="n">
-        <v>48</v>
+        <v>74</v>
       </c>
       <c r="I90" t="n">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="J90" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K90" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L90" t="n">
         <v>0</v>
@@ -6655,25 +6655,25 @@
         <v>1</v>
       </c>
       <c r="O90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P90" t="n">
-        <v>0.288659793814433</v>
+        <v>0.7717391304347826</v>
       </c>
       <c r="Q90" t="n">
-        <v>0</v>
+        <v>1.492307692307692</v>
       </c>
       <c r="R90" t="n">
-        <v>0.8571428571428571</v>
+        <v>1.057142857142857</v>
       </c>
       <c r="S90" t="n">
-        <v>5.003020844956901</v>
+        <v>5.941544227089326</v>
       </c>
       <c r="T90" t="n">
         <v>1</v>
       </c>
       <c r="U90" t="n">
-        <v>0.8005038219270155</v>
+        <v>0.9913679558518373</v>
       </c>
     </row>
     <row r="91">
@@ -6688,34 +6688,34 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>645859</v>
+        <v>696547</v>
       </c>
       <c r="D91" t="n">
-        <v>1</v>
+        <v>97</v>
       </c>
       <c r="E91" t="n">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="F91" t="n">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="G91" t="n">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="H91" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I91" t="n">
-        <v>39</v>
+        <v>78</v>
       </c>
       <c r="J91" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K91" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L91" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M91" t="n">
         <v>1</v>
@@ -6724,25 +6724,25 @@
         <v>0</v>
       </c>
       <c r="O91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P91" t="n">
-        <v>0.01333333333333333</v>
+        <v>1.021052631578947</v>
       </c>
       <c r="Q91" t="n">
-        <v>1.216666666666667</v>
+        <v>1.170212765957447</v>
       </c>
       <c r="R91" t="n">
-        <v>0.4102564102564102</v>
+        <v>0.2692307692307692</v>
       </c>
       <c r="S91" t="n">
-        <v>5.810138388247736</v>
+        <v>5.842951049570963</v>
       </c>
       <c r="T91" t="n">
         <v>1</v>
       </c>
       <c r="U91" t="n">
-        <v>0.7740726193858424</v>
+        <v>0.9859029088749611</v>
       </c>
     </row>
     <row r="92">
@@ -6757,61 +6757,61 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>976763</v>
+        <v>439603</v>
       </c>
       <c r="D92" t="n">
-        <v>90</v>
+        <v>62</v>
       </c>
       <c r="E92" t="n">
-        <v>77</v>
+        <v>43</v>
       </c>
       <c r="F92" t="n">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="G92" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="H92" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="I92" t="n">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="J92" t="n">
         <v>4</v>
       </c>
       <c r="K92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N92" t="n">
         <v>1</v>
       </c>
       <c r="O92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P92" t="n">
-        <v>1.168831168831169</v>
+        <v>1.441860465116279</v>
       </c>
       <c r="Q92" t="n">
-        <v>1.3125</v>
+        <v>1.761904761904762</v>
       </c>
       <c r="R92" t="n">
-        <v>2.631578947368421</v>
+        <v>0.1063829787234043</v>
       </c>
       <c r="S92" t="n">
-        <v>5.989789644702733</v>
+        <v>5.643061635457604</v>
       </c>
       <c r="T92" t="n">
         <v>1</v>
       </c>
       <c r="U92" t="n">
-        <v>0.9880736842916051</v>
+        <v>0.9857630688338351</v>
       </c>
     </row>
     <row r="93">
@@ -6826,61 +6826,61 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>384202</v>
+        <v>996543</v>
       </c>
       <c r="D93" t="n">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="E93" t="n">
-        <v>43</v>
+        <v>12</v>
       </c>
       <c r="F93" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="G93" t="n">
-        <v>37</v>
+        <v>96</v>
       </c>
       <c r="H93" t="n">
-        <v>94</v>
+        <v>66</v>
       </c>
       <c r="I93" t="n">
-        <v>46</v>
+        <v>12</v>
       </c>
       <c r="J93" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="K93" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L93" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O93" t="n">
         <v>1</v>
       </c>
       <c r="P93" t="n">
-        <v>1.953488372093023</v>
+        <v>7.916666666666667</v>
       </c>
       <c r="Q93" t="n">
-        <v>1.243243243243243</v>
+        <v>0.5208333333333334</v>
       </c>
       <c r="R93" t="n">
-        <v>2.043478260869565</v>
+        <v>5.5</v>
       </c>
       <c r="S93" t="n">
-        <v>5.584560751671846</v>
+        <v>5.998496478686624</v>
       </c>
       <c r="T93" t="n">
         <v>1</v>
       </c>
       <c r="U93" t="n">
-        <v>0.982305695754997</v>
+        <v>0.9186541473056584</v>
       </c>
     </row>
     <row r="94">
@@ -6895,61 +6895,61 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>670485</v>
+        <v>408549</v>
       </c>
       <c r="D94" t="n">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="E94" t="n">
-        <v>59</v>
+        <v>17</v>
       </c>
       <c r="F94" t="n">
-        <v>28</v>
+        <v>90</v>
       </c>
       <c r="G94" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="H94" t="n">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="I94" t="n">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="J94" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L94" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
       </c>
       <c r="P94" t="n">
-        <v>1.305084745762712</v>
+        <v>3.764705882352941</v>
       </c>
       <c r="Q94" t="n">
-        <v>9.333333333333334</v>
+        <v>3.75</v>
       </c>
       <c r="R94" t="n">
-        <v>0.686046511627907</v>
+        <v>0.6868686868686869</v>
       </c>
       <c r="S94" t="n">
-        <v>5.826389714050073</v>
+        <v>5.611245214834831</v>
       </c>
       <c r="T94" t="n">
         <v>1</v>
       </c>
       <c r="U94" t="n">
-        <v>0.9657578150181325</v>
+        <v>0.8790608000265715</v>
       </c>
     </row>
     <row r="95">
@@ -6964,61 +6964,61 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>166130</v>
+        <v>827834</v>
       </c>
       <c r="D95" t="n">
-        <v>59</v>
+        <v>17</v>
       </c>
       <c r="E95" t="n">
-        <v>88</v>
+        <v>23</v>
       </c>
       <c r="F95" t="n">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="G95" t="n">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="H95" t="n">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="I95" t="n">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="J95" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="K95" t="n">
         <v>2</v>
       </c>
       <c r="L95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O95" t="n">
         <v>1</v>
       </c>
       <c r="P95" t="n">
-        <v>0.6704545454545454</v>
+        <v>0.7391304347826086</v>
       </c>
       <c r="Q95" t="n">
-        <v>0.5641025641025641</v>
+        <v>1.188679245283019</v>
       </c>
       <c r="R95" t="n">
-        <v>2.363636363636364</v>
+        <v>1.488372093023256</v>
       </c>
       <c r="S95" t="n">
-        <v>5.220450679247016</v>
+        <v>5.917943783970437</v>
       </c>
       <c r="T95" t="n">
         <v>1</v>
       </c>
       <c r="U95" t="n">
-        <v>0.9851935511804782</v>
+        <v>0.5599447704563998</v>
       </c>
     </row>
     <row r="96">
@@ -7033,61 +7033,61 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>300770</v>
+        <v>2688</v>
       </c>
       <c r="D96" t="n">
-        <v>73</v>
+        <v>43</v>
       </c>
       <c r="E96" t="n">
-        <v>98</v>
+        <v>2</v>
       </c>
       <c r="F96" t="n">
-        <v>61</v>
+        <v>91</v>
       </c>
       <c r="G96" t="n">
-        <v>94</v>
+        <v>42</v>
       </c>
       <c r="H96" t="n">
-        <v>94</v>
+        <v>14</v>
       </c>
       <c r="I96" t="n">
-        <v>1</v>
+        <v>51</v>
       </c>
       <c r="J96" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="K96" t="n">
         <v>0</v>
       </c>
       <c r="L96" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
       </c>
       <c r="P96" t="n">
-        <v>0.7448979591836735</v>
+        <v>21.5</v>
       </c>
       <c r="Q96" t="n">
-        <v>0.648936170212766</v>
+        <v>2.166666666666667</v>
       </c>
       <c r="R96" t="n">
-        <v>94</v>
+        <v>0.2745098039215687</v>
       </c>
       <c r="S96" t="n">
-        <v>5.478235959754939</v>
+        <v>3.429590802223302</v>
       </c>
       <c r="T96" t="n">
         <v>1</v>
       </c>
       <c r="U96" t="n">
-        <v>0.8398228663537295</v>
+        <v>0.7046203135156013</v>
       </c>
     </row>
     <row r="97">
@@ -7102,61 +7102,61 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>65689</v>
+        <v>950075</v>
       </c>
       <c r="D97" t="n">
-        <v>7</v>
+        <v>78</v>
       </c>
       <c r="E97" t="n">
-        <v>58</v>
+        <v>26</v>
       </c>
       <c r="F97" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="G97" t="n">
-        <v>18</v>
+        <v>64</v>
       </c>
       <c r="H97" t="n">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="I97" t="n">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="J97" t="n">
         <v>9</v>
       </c>
       <c r="K97" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L97" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M97" t="n">
         <v>0</v>
       </c>
       <c r="N97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P97" t="n">
-        <v>0.1206896551724138</v>
+        <v>3</v>
       </c>
       <c r="Q97" t="n">
-        <v>1.222222222222222</v>
+        <v>0.015625</v>
       </c>
       <c r="R97" t="n">
-        <v>0.4918032786885246</v>
+        <v>0.9795918367346939</v>
       </c>
       <c r="S97" t="n">
-        <v>4.817499261867758</v>
+        <v>5.977758347457732</v>
       </c>
       <c r="T97" t="n">
         <v>1</v>
       </c>
       <c r="U97" t="n">
-        <v>0.7755270266568247</v>
+        <v>0.8932935533052039</v>
       </c>
     </row>
     <row r="98">
@@ -7171,37 +7171,37 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>354854</v>
+        <v>85314</v>
       </c>
       <c r="D98" t="n">
-        <v>58</v>
+        <v>29</v>
       </c>
       <c r="E98" t="n">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="F98" t="n">
-        <v>9</v>
+        <v>76</v>
       </c>
       <c r="G98" t="n">
-        <v>93</v>
+        <v>62</v>
       </c>
       <c r="H98" t="n">
-        <v>53</v>
+        <v>99</v>
       </c>
       <c r="I98" t="n">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="J98" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K98" t="n">
         <v>2</v>
       </c>
       <c r="L98" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N98" t="n">
         <v>1</v>
@@ -7210,22 +7210,22 @@
         <v>1</v>
       </c>
       <c r="P98" t="n">
-        <v>2.071428571428572</v>
+        <v>4.833333333333333</v>
       </c>
       <c r="Q98" t="n">
-        <v>0.09677419354838709</v>
+        <v>1.225806451612903</v>
       </c>
       <c r="R98" t="n">
-        <v>1</v>
+        <v>2.475</v>
       </c>
       <c r="S98" t="n">
-        <v>5.550050928931149</v>
+        <v>4.931025395112608</v>
       </c>
       <c r="T98" t="n">
         <v>1</v>
       </c>
       <c r="U98" t="n">
-        <v>0.9483477626330812</v>
+        <v>0.8150020099207054</v>
       </c>
     </row>
     <row r="99">
@@ -7240,61 +7240,61 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>577009</v>
+        <v>765664</v>
       </c>
       <c r="D99" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E99" t="n">
-        <v>69</v>
+        <v>47</v>
       </c>
       <c r="F99" t="n">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="G99" t="n">
-        <v>40</v>
+        <v>63</v>
       </c>
       <c r="H99" t="n">
+        <v>74</v>
+      </c>
+      <c r="I99" t="n">
         <v>62</v>
       </c>
-      <c r="I99" t="n">
-        <v>5</v>
-      </c>
       <c r="J99" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K99" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L99" t="n">
         <v>1</v>
       </c>
       <c r="M99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
       </c>
       <c r="P99" t="n">
-        <v>0.1449275362318841</v>
+        <v>0.1702127659574468</v>
       </c>
       <c r="Q99" t="n">
-        <v>1.625</v>
+        <v>0.5396825396825397</v>
       </c>
       <c r="R99" t="n">
-        <v>12.4</v>
+        <v>1.193548387096774</v>
       </c>
       <c r="S99" t="n">
-        <v>5.761183339857959</v>
+        <v>5.884038795122828</v>
       </c>
       <c r="T99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U99" t="n">
-        <v>0.8826476184860969</v>
+        <v>0.3607285010268943</v>
       </c>
     </row>
     <row r="100">
@@ -7309,25 +7309,25 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>995310</v>
+        <v>39975</v>
       </c>
       <c r="D100" t="n">
-        <v>15</v>
+        <v>90</v>
       </c>
       <c r="E100" t="n">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="F100" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G100" t="n">
-        <v>37</v>
+        <v>62</v>
       </c>
       <c r="H100" t="n">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="I100" t="n">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="J100" t="n">
         <v>8</v>
@@ -7336,34 +7336,34 @@
         <v>0</v>
       </c>
       <c r="L100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P100" t="n">
-        <v>0.2941176470588235</v>
+        <v>2.368421052631579</v>
       </c>
       <c r="Q100" t="n">
-        <v>0.02702702702702703</v>
+        <v>0.1129032258064516</v>
       </c>
       <c r="R100" t="n">
-        <v>0.32</v>
+        <v>1.081967213114754</v>
       </c>
       <c r="S100" t="n">
-        <v>5.997958803841233</v>
+        <v>4.601799336434531</v>
       </c>
       <c r="T100" t="n">
         <v>1</v>
       </c>
       <c r="U100" t="n">
-        <v>0.8568901450455195</v>
+        <v>0.8306784690522531</v>
       </c>
     </row>
     <row r="101">
@@ -7378,37 +7378,37 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>16854</v>
+        <v>336665</v>
       </c>
       <c r="D101" t="n">
-        <v>93</v>
+        <v>13</v>
       </c>
       <c r="E101" t="n">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="F101" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="G101" t="n">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="H101" t="n">
-        <v>24</v>
+        <v>63</v>
       </c>
       <c r="I101" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J101" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="K101" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L101" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N101" t="n">
         <v>1</v>
@@ -7417,22 +7417,22 @@
         <v>1</v>
       </c>
       <c r="P101" t="n">
-        <v>1.223684210526316</v>
+        <v>0.1444444444444444</v>
       </c>
       <c r="Q101" t="n">
-        <v>0.5</v>
+        <v>1.764705882352941</v>
       </c>
       <c r="R101" t="n">
-        <v>0.631578947368421</v>
+        <v>1.465116279069767</v>
       </c>
       <c r="S101" t="n">
-        <v>4.226728756856991</v>
+        <v>5.527199259073056</v>
       </c>
       <c r="T101" t="n">
         <v>1</v>
       </c>
       <c r="U101" t="n">
-        <v>0.9627367606226342</v>
+        <v>0.9093334550552385</v>
       </c>
     </row>
   </sheetData>
